--- a/method1_results.xlsx
+++ b/method1_results.xlsx
@@ -11,25 +11,33 @@
     <sheet name="NH4" sheetId="2" r:id="rId2"/>
     <sheet name="Cl" sheetId="3" r:id="rId3"/>
     <sheet name="Ni" sheetId="4" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" r:id="rId5"/>
+    <sheet name="Zn" sheetId="5" r:id="rId5"/>
+    <sheet name="Co" sheetId="6" r:id="rId6"/>
+    <sheet name="Mo" sheetId="7" r:id="rId7"/>
+    <sheet name="SO4" sheetId="8" r:id="rId8"/>
+    <sheet name="Ca" sheetId="9" r:id="rId9"/>
+    <sheet name="NO3" sheetId="10" r:id="rId10"/>
+    <sheet name="As" sheetId="11" r:id="rId11"/>
+    <sheet name="Cr" sheetId="12" r:id="rId12"/>
+    <sheet name="Summary" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="44">
   <si>
-    <t>Year</t>
+    <t>Period</t>
   </si>
   <si>
     <t>Season</t>
   </si>
   <si>
-    <t>Actual (ug/L)</t>
+    <t>Actual (µg/L)</t>
   </si>
   <si>
-    <t>Method1 (ug/L)</t>
+    <t>Method1 (µg/L)</t>
   </si>
   <si>
     <t>Difference</t>
@@ -44,7 +52,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>Cu — Mass-Balance LK Model  |  Mix: 50% Lev / 50% Kir</t>
+    <t>Cu — Mass-Balance LK (corrected model)</t>
   </si>
   <si>
     <t>Actual (mg/L)</t>
@@ -53,13 +61,37 @@
     <t>Method1 (mg/L)</t>
   </si>
   <si>
-    <t>NH4 — Mass-Balance LK Model  |  Mix: 50% Lev / 50% Kir</t>
+    <t>NH4 — Mass-Balance LK (corrected model)</t>
   </si>
   <si>
-    <t>Cl — Mass-Balance LK Model  |  Mix: 50% Lev / 50% Kir</t>
+    <t>Cl — Mass-Balance LK (corrected model)</t>
   </si>
   <si>
-    <t>Ni — Mass-Balance LK Model  |  Mix: 50% Lev / 50% Kir</t>
+    <t>Ni — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>Zn — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>Co — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>Mo — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>SO4 — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>Ca — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>NO3 — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>As — Mass-Balance LK (corrected model)</t>
+  </si>
+  <si>
+    <t>Cr — Mass-Balance LK (corrected model)</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -68,10 +100,10 @@
     <t>Unit</t>
   </si>
   <si>
-    <t>Mix</t>
+    <t>Lev rate (g/ton)</t>
   </si>
   <si>
-    <t>LK leach rate</t>
+    <t>Kir rate (g/ton)</t>
   </si>
   <si>
     <t>MAE</t>
@@ -80,7 +112,7 @@
     <t>RMSE</t>
   </si>
   <si>
-    <t>Validation periods</t>
+    <t>n_valid</t>
   </si>
   <si>
     <t>Cu</t>
@@ -95,16 +127,37 @@
     <t>Ni</t>
   </si>
   <si>
-    <t>ug/L</t>
+    <t>Zn</t>
+  </si>
+  <si>
+    <t>Co</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>SO4</t>
+  </si>
+  <si>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>NO3</t>
+  </si>
+  <si>
+    <t>As</t>
+  </si>
+  <si>
+    <t>Cr</t>
+  </si>
+  <si>
+    <t>µg/L</t>
   </si>
   <si>
     <t>mg/L</t>
   </si>
   <si>
-    <t>50% Lev / 50% Kir</t>
-  </si>
-  <si>
-    <t>Mass-Balance Model Validation Summary</t>
+    <t>Mass-Balance Model — Validation Summary</t>
   </si>
 </sst>
 </file>
@@ -519,10 +572,10 @@
         <v>2.14</v>
       </c>
       <c r="D4" s="3">
-        <v>0.8844</v>
+        <v>2.9316</v>
       </c>
       <c r="E4" s="3">
-        <v>-1.2556</v>
+        <v>0.7916</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -536,10 +589,10 @@
         <v>3.024</v>
       </c>
       <c r="D5" s="3">
-        <v>0.9787</v>
+        <v>3.5903</v>
       </c>
       <c r="E5" s="3">
-        <v>-2.0453</v>
+        <v>0.5663</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -553,10 +606,10 @@
         <v>2.8667</v>
       </c>
       <c r="D6" s="3">
-        <v>0.7291</v>
+        <v>3.7874</v>
       </c>
       <c r="E6" s="3">
-        <v>-2.1376</v>
+        <v>0.9207</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -570,10 +623,10 @@
         <v>2.46</v>
       </c>
       <c r="D7" s="3">
-        <v>0.8545</v>
+        <v>3.9903</v>
       </c>
       <c r="E7" s="3">
-        <v>-1.6055</v>
+        <v>1.5303</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -587,10 +640,10 @@
         <v>1.924</v>
       </c>
       <c r="D8" s="3">
-        <v>0.6075</v>
+        <v>4.5543</v>
       </c>
       <c r="E8" s="3">
-        <v>-1.3165</v>
+        <v>2.6303</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -604,10 +657,10 @@
         <v>2.3333</v>
       </c>
       <c r="D9" s="3">
-        <v>0.6972</v>
+        <v>5.0194</v>
       </c>
       <c r="E9" s="3">
-        <v>-1.6361</v>
+        <v>2.6861</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -621,10 +674,10 @@
         <v>3.1575</v>
       </c>
       <c r="D10" s="3">
-        <v>0.5983000000000001</v>
+        <v>5.1173</v>
       </c>
       <c r="E10" s="3">
-        <v>-2.5592</v>
+        <v>1.9598</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -638,10 +691,10 @@
         <v>2.625</v>
       </c>
       <c r="D11" s="3">
-        <v>0.6967</v>
+        <v>5.2327</v>
       </c>
       <c r="E11" s="3">
-        <v>-1.9283</v>
+        <v>2.6077</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -655,10 +708,10 @@
         <v>1.9733</v>
       </c>
       <c r="D12" s="3">
-        <v>0.2312</v>
+        <v>5.4164</v>
       </c>
       <c r="E12" s="3">
-        <v>-1.7422</v>
+        <v>3.4431</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -672,10 +725,10 @@
         <v>2.308</v>
       </c>
       <c r="D13" s="3">
-        <v>0.1896</v>
+        <v>5.5543</v>
       </c>
       <c r="E13" s="3">
-        <v>-2.1184</v>
+        <v>3.2463</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -689,10 +742,10 @@
         <v>1.9525</v>
       </c>
       <c r="D14" s="3">
-        <v>0.196</v>
+        <v>4.9556</v>
       </c>
       <c r="E14" s="3">
-        <v>-1.7565</v>
+        <v>3.0031</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -706,10 +759,10 @@
         <v>1.8125</v>
       </c>
       <c r="D15" s="3">
-        <v>0.1877</v>
+        <v>4.5066</v>
       </c>
       <c r="E15" s="3">
-        <v>-1.6248</v>
+        <v>2.6941</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -723,10 +776,10 @@
         <v>2.46</v>
       </c>
       <c r="D16" s="3">
-        <v>0.6277</v>
+        <v>5.0648</v>
       </c>
       <c r="E16" s="3">
-        <v>-1.8323</v>
+        <v>2.6048</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -740,10 +793,10 @@
         <v>1.7267</v>
       </c>
       <c r="D17" s="3">
-        <v>0.7756</v>
+        <v>5.5352</v>
       </c>
       <c r="E17" s="3">
-        <v>-0.9510999999999999</v>
+        <v>3.8085</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -757,10 +810,10 @@
         <v>1.7667</v>
       </c>
       <c r="D18" s="3">
-        <v>0.6677</v>
+        <v>5.5504</v>
       </c>
       <c r="E18" s="3">
-        <v>-1.099</v>
+        <v>3.7837</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -774,10 +827,10 @@
         <v>1.8217</v>
       </c>
       <c r="D19" s="3">
-        <v>0.7858000000000001</v>
+        <v>5.6166</v>
       </c>
       <c r="E19" s="3">
-        <v>-1.0358</v>
+        <v>3.7949</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -791,10 +844,10 @@
         <v>2.09</v>
       </c>
       <c r="D20" s="3">
-        <v>0.6683</v>
+        <v>5.2034</v>
       </c>
       <c r="E20" s="3">
-        <v>-1.4217</v>
+        <v>3.1134</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -808,10 +861,10 @@
         <v>2.1525</v>
       </c>
       <c r="D21" s="3">
-        <v>0.7859</v>
+        <v>4.9353</v>
       </c>
       <c r="E21" s="3">
-        <v>-1.3666</v>
+        <v>2.7828</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -825,10 +878,10 @@
         <v>1.99</v>
       </c>
       <c r="D22" s="3">
-        <v>0.8042</v>
+        <v>4.6255</v>
       </c>
       <c r="E22" s="3">
-        <v>-1.1858</v>
+        <v>2.6355</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -842,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>0.8042</v>
+        <v>4.7787</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -859,7 +912,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>0.9709</v>
+        <v>4.9584</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -876,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>0.8139</v>
+        <v>5.0284</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -893,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>0.9714</v>
+        <v>5.1456</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -910,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>0.8139</v>
+        <v>5.1688</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -927,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>0.9714</v>
+        <v>5.2509</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -944,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>0.8139</v>
+        <v>5.2478</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -961,7 +1014,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>0.9714</v>
+        <v>5.3102</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -978,10 +1031,1832 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>0.8139</v>
+        <v>5.2922</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10.5967</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10.0272</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-0.5695</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3.628</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10.2954</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6.6674</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8.9633</v>
+      </c>
+      <c r="D6" s="3">
+        <v>9.4741</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.5108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>5.1267</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9.4466</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4.3199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>10.686</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.461600000000001</v>
+      </c>
+      <c r="E8" s="3">
+        <v>-2.2244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.5067</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.1723</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1.6656</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5.988</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.4767</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.4887</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.3967</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.4044</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.0077</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9.0083</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.8143</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-3.194</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4.98</v>
+      </c>
+      <c r="D13" s="3">
+        <v>4.6217</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-0.3583</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>7.145</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.648</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-3.497</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4.2125</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.9177</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-1.2948</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4.34</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.81</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5.17</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4.8507</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-0.3193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>9.01</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5.0478</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3.9622</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4.0483</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5.6577</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.6094</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5.25</v>
+      </c>
+      <c r="D20" s="3">
+        <v>5.6762</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.4262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>3.335</v>
+      </c>
+      <c r="D21" s="3">
+        <v>6.1897</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2.8547</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>4.7133</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.383</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.8089</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.4259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.314</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.4778</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.1638</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.3912</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.9008</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.5096</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.3427</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4.7253</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4.3826</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.4622</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4.5374</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4.0752</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.395</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4.784</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4.389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4.5854</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4.3674</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.466</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4.824</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.3383</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.6439</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.3056</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.2672</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.7589</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.4917</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.379</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.0921</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.7131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.3395</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.592</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.2525</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.2415</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.4179</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.1764</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.296</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.5131</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.2171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.3203</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.8662</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3.5459</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.313</v>
+      </c>
+      <c r="D19" s="3">
+        <v>4.635</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4.322</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D20" s="3">
+        <v>4.4689</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4.2189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.3063</v>
+      </c>
+      <c r="D21" s="3">
+        <v>4.7291</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4.4228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.1853</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5.6066</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5.4213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5.7236</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>6.408</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>6.3247</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>6.8589</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>6.6629</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.1125</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>6.8531</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>7.2551</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>6.96</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.0489</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.0635</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.0146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.0542</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.0823</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.0281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.1239</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.0852</v>
+      </c>
+      <c r="E6" s="3">
+        <v>-0.0387</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.094</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.0825</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.0882</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.0057</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.089</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-0.0072</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.0511</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.0843</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.0332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.089</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.0859</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-0.0031</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.0876</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.0713</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-0.0163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.0726</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.0604</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-0.0122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.06859999999999999</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.0502</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-0.0184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.0761</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.0425</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-0.0336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.0574</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.0559</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-0.0015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.0403</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.0722</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.0319</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.0573</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.076</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.0187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.0626</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.0854</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.0228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.0621</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.0824</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.0204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.0464</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.0852</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.0388</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.037</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.0961</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.0591</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.0977</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.1067</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.1057</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.1127</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.1102</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.116</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.1127</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.1179</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.1141</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4">
+        <v>0.001357778</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2.5581</v>
+      </c>
+      <c r="F4">
+        <v>2.7335</v>
+      </c>
+      <c r="G4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0.1262</v>
+      </c>
+      <c r="F5">
+        <v>0.1452</v>
+      </c>
+      <c r="G5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>154.4444</v>
+      </c>
+      <c r="D6">
+        <v>285.4063</v>
+      </c>
+      <c r="E6">
+        <v>48.5367</v>
+      </c>
+      <c r="F6">
+        <v>57.2457</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>0.000631333</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0.4808</v>
+      </c>
+      <c r="F7">
+        <v>0.5582</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8">
+        <v>0.005306667</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3.7708</v>
+      </c>
+      <c r="F8">
+        <v>3.9845</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>0.000106889</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0.1824</v>
+      </c>
+      <c r="F9">
+        <v>0.2062</v>
+      </c>
+      <c r="G9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10">
+        <v>0.022955556</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>3.5569</v>
+      </c>
+      <c r="F10">
+        <v>4.3939</v>
+      </c>
+      <c r="G10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11">
+        <v>260</v>
+      </c>
+      <c r="D11">
+        <v>1653.9055</v>
+      </c>
+      <c r="E11">
+        <v>286.5115</v>
+      </c>
+      <c r="F11">
+        <v>352.0667</v>
+      </c>
+      <c r="G11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>141.7778</v>
+      </c>
+      <c r="D12">
+        <v>581.4258</v>
+      </c>
+      <c r="E12">
+        <v>111.1493</v>
+      </c>
+      <c r="F12">
+        <v>132.071</v>
+      </c>
+      <c r="G12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>17.2775</v>
+      </c>
+      <c r="G13">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>0.012511111</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>3.461</v>
+      </c>
+      <c r="F14">
+        <v>3.6436</v>
+      </c>
+      <c r="G14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15">
+        <v>0.000163111</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0.0241</v>
+      </c>
+      <c r="F15">
+        <v>0.0288</v>
+      </c>
+      <c r="G15">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1030,10 +2905,10 @@
         <v>0.1792</v>
       </c>
       <c r="D4" s="3">
-        <v>118.4514</v>
+        <v>0.1624</v>
       </c>
       <c r="E4" s="3">
-        <v>118.2723</v>
+        <v>-0.0168</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1047,10 +2922,10 @@
         <v>0.0291</v>
       </c>
       <c r="D5" s="3">
-        <v>162.4671</v>
+        <v>0.1497</v>
       </c>
       <c r="E5" s="3">
-        <v>162.438</v>
+        <v>0.1206</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1064,10 +2939,10 @@
         <v>0.1017</v>
       </c>
       <c r="D6" s="3">
-        <v>109.7004</v>
+        <v>0.1345</v>
       </c>
       <c r="E6" s="3">
-        <v>109.5986</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1081,10 +2956,10 @@
         <v>0.0218</v>
       </c>
       <c r="D7" s="3">
-        <v>138.0349</v>
+        <v>0.123</v>
       </c>
       <c r="E7" s="3">
-        <v>138.0131</v>
+        <v>0.1012</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1098,10 +2973,10 @@
         <v>0.1515</v>
       </c>
       <c r="D8" s="3">
-        <v>84.6114</v>
+        <v>0.1125</v>
       </c>
       <c r="E8" s="3">
-        <v>84.4599</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1115,10 +2990,10 @@
         <v>0.0113</v>
       </c>
       <c r="D9" s="3">
-        <v>105.4858</v>
+        <v>0.1046</v>
       </c>
       <c r="E9" s="3">
-        <v>105.4745</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1132,10 +3007,10 @@
         <v>0.0765</v>
       </c>
       <c r="D10" s="3">
-        <v>82.7193</v>
+        <v>0.1241</v>
       </c>
       <c r="E10" s="3">
-        <v>82.64279999999999</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1149,10 +3024,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" s="3">
-        <v>105.3823</v>
+        <v>0.1388</v>
       </c>
       <c r="E11" s="3">
-        <v>105.3483</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1166,10 +3041,10 @@
         <v>0.0917</v>
       </c>
       <c r="D12" s="3">
-        <v>6.1547</v>
+        <v>0.1784</v>
       </c>
       <c r="E12" s="3">
-        <v>6.063</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1183,10 +3058,10 @@
         <v>0.0177</v>
       </c>
       <c r="D13" s="3">
-        <v>0.3976</v>
+        <v>0.2082</v>
       </c>
       <c r="E13" s="3">
-        <v>0.3799</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1197,13 +3072,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="3">
-        <v>0.07779999999999999</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="D14" s="3">
-        <v>0.08840000000000001</v>
+        <v>0.1885</v>
       </c>
       <c r="E14" s="3">
-        <v>0.0106</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1217,10 +3092,10 @@
         <v>0.037</v>
       </c>
       <c r="D15" s="3">
-        <v>0.0658</v>
+        <v>0.1737</v>
       </c>
       <c r="E15" s="3">
-        <v>0.0288</v>
+        <v>0.1367</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1234,10 +3109,10 @@
         <v>0.11</v>
       </c>
       <c r="D16" s="3">
-        <v>88.12479999999999</v>
+        <v>0.1712</v>
       </c>
       <c r="E16" s="3">
-        <v>88.01479999999999</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1251,10 +3126,10 @@
         <v>0.0092</v>
       </c>
       <c r="D17" s="3">
-        <v>121.6676</v>
+        <v>0.1692</v>
       </c>
       <c r="E17" s="3">
-        <v>121.6584</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1268,10 +3143,10 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="D18" s="3">
-        <v>97.2486</v>
+        <v>0.2338</v>
       </c>
       <c r="E18" s="3">
-        <v>97.1713</v>
+        <v>0.1565</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1285,10 +3160,10 @@
         <v>0.0403</v>
       </c>
       <c r="D19" s="3">
-        <v>123.8399</v>
+        <v>0.2822</v>
       </c>
       <c r="E19" s="3">
-        <v>123.7995</v>
+        <v>0.2419</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1302,10 +3177,10 @@
         <v>0.0625</v>
       </c>
       <c r="D20" s="3">
-        <v>97.0402</v>
+        <v>0.267</v>
       </c>
       <c r="E20" s="3">
-        <v>96.9777</v>
+        <v>0.2045</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1319,10 +3194,10 @@
         <v>0.012</v>
       </c>
       <c r="D21" s="3">
-        <v>123.8285</v>
+        <v>0.2556</v>
       </c>
       <c r="E21" s="3">
-        <v>123.8165</v>
+        <v>0.2436</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1336,10 +3211,10 @@
         <v>0.0406</v>
       </c>
       <c r="D22" s="3">
-        <v>126.1941</v>
+        <v>0.2908</v>
       </c>
       <c r="E22" s="3">
-        <v>126.1535</v>
+        <v>0.2502</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1353,7 +3228,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>125.2347</v>
+        <v>0.2703</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -1370,7 +3245,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>162.1242</v>
+        <v>0.2548</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -1387,7 +3262,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>127.3234</v>
+        <v>0.2433</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -1404,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>162.2384</v>
+        <v>0.2346</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -1421,7 +3296,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>127.33</v>
+        <v>0.2281</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -1438,7 +3313,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>162.2388</v>
+        <v>0.2232</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -1455,7 +3330,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>127.33</v>
+        <v>0.2195</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -1472,7 +3347,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>162.2388</v>
+        <v>0.2168</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -1489,7 +3364,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>127.33</v>
+        <v>0.2147</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -1541,10 +3416,10 @@
         <v>152.3333</v>
       </c>
       <c r="D4" s="3">
-        <v>11480.8597</v>
+        <v>165.1339</v>
       </c>
       <c r="E4" s="3">
-        <v>11328.5263</v>
+        <v>12.8006</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1558,10 +3433,10 @@
         <v>87.98</v>
       </c>
       <c r="D5" s="3">
-        <v>15739.0043</v>
+        <v>193.619</v>
       </c>
       <c r="E5" s="3">
-        <v>15651.0243</v>
+        <v>105.639</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1575,10 +3450,10 @@
         <v>115.05</v>
       </c>
       <c r="D6" s="3">
-        <v>10625.0621</v>
+        <v>188.8659</v>
       </c>
       <c r="E6" s="3">
-        <v>10510.0121</v>
+        <v>73.8159</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1592,10 +3467,10 @@
         <v>104.1333</v>
       </c>
       <c r="D7" s="3">
-        <v>13371.443</v>
+        <v>201.2847</v>
       </c>
       <c r="E7" s="3">
-        <v>13267.3096</v>
+        <v>97.1514</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1609,10 +3484,10 @@
         <v>139.4</v>
       </c>
       <c r="D8" s="3">
-        <v>8194.280500000001</v>
+        <v>185.3351</v>
       </c>
       <c r="E8" s="3">
-        <v>8054.8805</v>
+        <v>45.9351</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1626,10 +3501,10 @@
         <v>125.7667</v>
       </c>
       <c r="D9" s="3">
-        <v>10217.9045</v>
+        <v>185.5807</v>
       </c>
       <c r="E9" s="3">
-        <v>10092.1379</v>
+        <v>59.814</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1640,13 +3515,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="3">
-        <v>98.6108</v>
+        <v>98.61069999999999</v>
       </c>
       <c r="D10" s="3">
-        <v>8010.964</v>
+        <v>174.2978</v>
       </c>
       <c r="E10" s="3">
-        <v>7912.3533</v>
+        <v>75.687</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1660,10 +3535,10 @@
         <v>130</v>
       </c>
       <c r="D11" s="3">
-        <v>10207.8784</v>
+        <v>178.0433</v>
       </c>
       <c r="E11" s="3">
-        <v>10077.8784</v>
+        <v>48.0433</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1677,10 +3552,10 @@
         <v>178.5</v>
       </c>
       <c r="D12" s="3">
-        <v>593.1807</v>
+        <v>138.2425</v>
       </c>
       <c r="E12" s="3">
-        <v>414.6807</v>
+        <v>-40.2575</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1694,10 +3569,10 @@
         <v>112.66</v>
       </c>
       <c r="D13" s="3">
-        <v>36.3844</v>
+        <v>108.392</v>
       </c>
       <c r="E13" s="3">
-        <v>-76.2756</v>
+        <v>-4.268</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1711,10 +3586,10 @@
         <v>150.25</v>
       </c>
       <c r="D14" s="3">
-        <v>4.9655</v>
+        <v>85.9472</v>
       </c>
       <c r="E14" s="3">
-        <v>-145.2845</v>
+        <v>-64.3028</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1728,10 +3603,10 @@
         <v>112.25</v>
       </c>
       <c r="D15" s="3">
-        <v>4.213</v>
+        <v>69.11360000000001</v>
       </c>
       <c r="E15" s="3">
-        <v>-108.037</v>
+        <v>-43.1364</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1745,10 +3620,10 @@
         <v>105</v>
       </c>
       <c r="D16" s="3">
-        <v>8534.9373</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="E16" s="3">
-        <v>8429.9373</v>
+        <v>-10.07</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1762,10 +3637,10 @@
         <v>129</v>
       </c>
       <c r="D17" s="3">
-        <v>11785.6971</v>
+        <v>126.3</v>
       </c>
       <c r="E17" s="3">
-        <v>11656.6971</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1779,10 +3654,10 @@
         <v>151</v>
       </c>
       <c r="D18" s="3">
-        <v>9418.569</v>
+        <v>133.4853</v>
       </c>
       <c r="E18" s="3">
-        <v>9267.569</v>
+        <v>-17.5147</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1796,10 +3671,10 @@
         <v>122.3333</v>
       </c>
       <c r="D19" s="3">
-        <v>11996.1412</v>
+        <v>152.7299</v>
       </c>
       <c r="E19" s="3">
-        <v>11873.8079</v>
+        <v>30.3966</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1813,10 +3688,10 @@
         <v>97.77500000000001</v>
       </c>
       <c r="D20" s="3">
-        <v>9398.511</v>
+        <v>151.3113</v>
       </c>
       <c r="E20" s="3">
-        <v>9300.736000000001</v>
+        <v>53.5363</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1830,10 +3705,10 @@
         <v>118</v>
       </c>
       <c r="D21" s="3">
-        <v>11995.0442</v>
+        <v>163.2509</v>
       </c>
       <c r="E21" s="3">
-        <v>11877.0442</v>
+        <v>45.2509</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1847,10 +3722,10 @@
         <v>99.5667</v>
       </c>
       <c r="D22" s="3">
-        <v>12222.7034</v>
+        <v>191.4454</v>
       </c>
       <c r="E22" s="3">
-        <v>12123.1367</v>
+        <v>91.87869999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1864,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>12130.0038</v>
+        <v>195.079</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -1881,7 +3756,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>15705.3391</v>
+        <v>216.6025</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -1898,7 +3773,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>12332.4508</v>
+        <v>213.9469</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -1915,7 +3790,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>15716.4116</v>
+        <v>230.7534</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -1932,7 +3807,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>12333.0944</v>
+        <v>224.56</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -1949,7 +3824,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>15716.4468</v>
+        <v>238.7132</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -1966,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>12333.0965</v>
+        <v>230.5299</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -1983,7 +3858,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>15716.4469</v>
+        <v>243.1906</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -2000,7 +3875,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>12333.0965</v>
+        <v>233.888</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -2052,10 +3927,10 @@
         <v>1.111</v>
       </c>
       <c r="D4" s="3">
-        <v>0.1892</v>
+        <v>0.9679</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.9218</v>
+        <v>-0.1431</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2069,10 +3944,10 @@
         <v>0.6304</v>
       </c>
       <c r="D5" s="3">
-        <v>0.1592</v>
+        <v>0.8908</v>
       </c>
       <c r="E5" s="3">
-        <v>-0.4712</v>
+        <v>0.2604</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2086,10 +3961,10 @@
         <v>1.027</v>
       </c>
       <c r="D6" s="3">
-        <v>0.121</v>
+        <v>0.7915</v>
       </c>
       <c r="E6" s="3">
-        <v>-0.906</v>
+        <v>-0.2355</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2103,10 +3978,10 @@
         <v>0.8773</v>
       </c>
       <c r="D7" s="3">
-        <v>0.1385</v>
+        <v>0.7426</v>
       </c>
       <c r="E7" s="3">
-        <v>-0.7388</v>
+        <v>-0.1347</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2120,10 +3995,10 @@
         <v>1.0592</v>
       </c>
       <c r="D8" s="3">
-        <v>0.103</v>
+        <v>0.6585</v>
       </c>
       <c r="E8" s="3">
-        <v>-0.9562</v>
+        <v>-0.4007</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2137,10 +4012,10 @@
         <v>0.632</v>
       </c>
       <c r="D9" s="3">
-        <v>0.1154</v>
+        <v>0.6149</v>
       </c>
       <c r="E9" s="3">
-        <v>-0.5165999999999999</v>
+        <v>-0.0171</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2151,13 +4026,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="3">
-        <v>1.1802</v>
+        <v>1.1803</v>
       </c>
       <c r="D10" s="3">
-        <v>0.1016</v>
+        <v>0.6041</v>
       </c>
       <c r="E10" s="3">
-        <v>-1.0786</v>
+        <v>-0.5762</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2171,10 +4046,10 @@
         <v>0.9045</v>
       </c>
       <c r="D11" s="3">
-        <v>0.1153</v>
+        <v>0.6155</v>
       </c>
       <c r="E11" s="3">
-        <v>-0.7892</v>
+        <v>-0.289</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2188,10 +4063,10 @@
         <v>1.4617</v>
       </c>
       <c r="D12" s="3">
-        <v>0.0489</v>
+        <v>0.5683</v>
       </c>
       <c r="E12" s="3">
-        <v>-1.4127</v>
+        <v>-0.8934</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2205,10 +4080,10 @@
         <v>0.9718</v>
       </c>
       <c r="D13" s="3">
-        <v>0.0409</v>
+        <v>0.533</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.9308999999999999</v>
+        <v>-0.4388</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2222,10 +4097,10 @@
         <v>1.4625</v>
       </c>
       <c r="D14" s="3">
-        <v>0.0412</v>
+        <v>0.4775</v>
       </c>
       <c r="E14" s="3">
-        <v>-1.4213</v>
+        <v>-0.985</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2239,10 +4114,10 @@
         <v>0.9625</v>
       </c>
       <c r="D15" s="3">
-        <v>0.0405</v>
+        <v>0.4358</v>
       </c>
       <c r="E15" s="3">
-        <v>-0.922</v>
+        <v>-0.5266999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2256,10 +4131,10 @@
         <v>1.395</v>
       </c>
       <c r="D16" s="3">
-        <v>0.1074</v>
+        <v>0.4988</v>
       </c>
       <c r="E16" s="3">
-        <v>-1.2876</v>
+        <v>-0.8962</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2273,10 +4148,10 @@
         <v>0.8877</v>
       </c>
       <c r="D17" s="3">
-        <v>0.127</v>
+        <v>0.57</v>
       </c>
       <c r="E17" s="3">
-        <v>-0.7607</v>
+        <v>-0.3177</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2290,10 +4165,10 @@
         <v>1.4013</v>
       </c>
       <c r="D18" s="3">
-        <v>0.1114</v>
+        <v>0.5627</v>
       </c>
       <c r="E18" s="3">
-        <v>-1.2899</v>
+        <v>-0.8386</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2307,10 +4182,10 @@
         <v>0.9702</v>
       </c>
       <c r="D19" s="3">
-        <v>0.1284</v>
+        <v>0.5827</v>
       </c>
       <c r="E19" s="3">
-        <v>-0.8418</v>
+        <v>-0.3875</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2324,10 +4199,10 @@
         <v>1.315</v>
       </c>
       <c r="D20" s="3">
-        <v>0.1122</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="E20" s="3">
-        <v>-1.2028</v>
+        <v>-0.7701</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2341,10 +4216,10 @@
         <v>0.8648</v>
       </c>
       <c r="D21" s="3">
-        <v>0.1284</v>
+        <v>0.5359</v>
       </c>
       <c r="E21" s="3">
-        <v>-0.7363</v>
+        <v>-0.3288</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2358,10 +4233,10 @@
         <v>1.2833</v>
       </c>
       <c r="D22" s="3">
-        <v>0.13</v>
+        <v>0.587</v>
       </c>
       <c r="E22" s="3">
-        <v>-1.1533</v>
+        <v>-0.6963</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2375,7 +4250,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>0.1318</v>
+        <v>0.5927</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -2392,7 +4267,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>0.1556</v>
+        <v>0.627</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -2409,7 +4284,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>0.1333</v>
+        <v>0.6227</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -2426,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>0.1557</v>
+        <v>0.6495</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -2443,7 +4318,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>0.1333</v>
+        <v>0.6395</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -2460,7 +4335,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>0.1557</v>
+        <v>0.6622</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -2477,7 +4352,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>0.1333</v>
+        <v>0.649</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -2494,7 +4369,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>0.1557</v>
+        <v>0.6693</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -2511,7 +4386,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>0.1333</v>
+        <v>0.6544</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -2524,131 +4399,2552 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.9397</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.3374</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.3977</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.1848</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4.6399</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.4551</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.6683</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5.3441</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.6758</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.0067</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.0875</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4.0808</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.674</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6.4764</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.8024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.9324</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4.4924</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>12.4875</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6.9366</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-5.5509</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.695</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.1042</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.4092</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>7.4933</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6.5689</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-0.9244</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.326</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6.1674</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.8414</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.6138</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.573</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3.9593</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5.1272</v>
+      </c>
+      <c r="E15" s="3">
+        <v>4.2577</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.1195</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5.4032</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.2837</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.1493</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5.8119</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5.6626</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5.8538</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.1708</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2.1857</v>
+      </c>
+      <c r="D19" s="3">
+        <v>6.099</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3.9133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2.251</v>
+      </c>
+      <c r="D20" s="3">
+        <v>5.8761</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.6251</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1.9467</v>
+      </c>
+      <c r="D21" s="3">
+        <v>5.8722</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.9255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1.221</v>
+      </c>
+      <c r="D22" s="3">
+        <v>6.4374</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5.2164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>6.6255</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>7.0196</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>7.0622</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>7.3471</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>7.3078</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.5313</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>7.4459</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>7.635</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.5237</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.2707</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.2399</v>
+      </c>
+      <c r="E4" s="3">
+        <v>-0.0308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.1318</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.222</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.0902</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.3793</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.1974</v>
+      </c>
+      <c r="E6" s="3">
+        <v>-0.1819</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.4023</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.1833</v>
+      </c>
+      <c r="E7" s="3">
+        <v>-0.219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.4892</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.1646</v>
+      </c>
+      <c r="E8" s="3">
+        <v>-0.3246</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.2327</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.1539</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-0.0788</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.4718</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.1569</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-0.3148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.2345</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.1624</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-0.0721</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.3962</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.1658</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-0.2304</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.324</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.1684</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-0.1556</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.3668</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.1584</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-0.2084</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.2775</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.1509</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-0.1266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.517</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.1679</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-0.3491</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.3653</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.1847</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-0.1806</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.409</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.1899</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-0.2191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.3383</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.198</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-0.1403</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.3935</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.1848</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-0.2087</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.1585</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.1782</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.0197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.5087</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.1938</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-0.3149</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.1907</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.1935</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.1905</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.1934</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.1904</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.1933</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.1904</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.1933</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.1903</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>12.47</v>
+      </c>
+      <c r="D4" s="3">
+        <v>13.1244</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.6544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>11.58</v>
+      </c>
+      <c r="D5" s="3">
+        <v>14.7149</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.1349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>13.52</v>
+      </c>
+      <c r="D6" s="3">
+        <v>14.3573</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.8373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>16.1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>15.0199</v>
+      </c>
+      <c r="E7" s="3">
+        <v>-1.0801</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>16.3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>13.9712</v>
+      </c>
+      <c r="E8" s="3">
+        <v>-2.3288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3">
+        <v>13.8956</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-5.1044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>11.03</v>
+      </c>
+      <c r="D10" s="3">
+        <v>13.2248</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.1948</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>13.4327</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-3.0673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>18.33</v>
+      </c>
+      <c r="D12" s="3">
+        <v>11.1995</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-7.1305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>15.02</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9.5246</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-5.4954</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>18.9</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.247</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-10.653</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>14.65</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7.2888</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-7.3612</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.9894</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-3.4106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>14.37</v>
+      </c>
+      <c r="D17" s="3">
+        <v>11.1377</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-3.2323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>14.17</v>
+      </c>
+      <c r="D18" s="3">
+        <v>11.7141</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2.4559</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>14.98</v>
+      </c>
+      <c r="D19" s="3">
+        <v>13.0712</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-1.9088</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>14.88</v>
+      </c>
+      <c r="D20" s="3">
+        <v>12.7205</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2.1595</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>12.65</v>
+      </c>
+      <c r="D21" s="3">
+        <v>13.1634</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.5134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>10.15</v>
+      </c>
+      <c r="D22" s="3">
+        <v>15.008</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4.858</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>15.1145</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>16.289</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>16.0752</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>17.0095</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>16.6156</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>17.4148</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>16.9195</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>17.6428</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>17.0905</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>498.6667</v>
+      </c>
+      <c r="D4" s="3">
+        <v>589.7595</v>
+      </c>
+      <c r="E4" s="3">
+        <v>91.0928</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>305.8</v>
+      </c>
+      <c r="D5" s="3">
+        <v>737.093</v>
+      </c>
+      <c r="E5" s="3">
+        <v>431.293</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>438.8333</v>
+      </c>
+      <c r="D6" s="3">
+        <v>738.1724</v>
+      </c>
+      <c r="E6" s="3">
+        <v>299.3391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>469.6667</v>
+      </c>
+      <c r="D7" s="3">
+        <v>805.8577</v>
+      </c>
+      <c r="E7" s="3">
+        <v>336.191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>597.6</v>
+      </c>
+      <c r="D8" s="3">
+        <v>750.2536</v>
+      </c>
+      <c r="E8" s="3">
+        <v>152.6536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>715.3333</v>
+      </c>
+      <c r="D9" s="3">
+        <v>759.628</v>
+      </c>
+      <c r="E9" s="3">
+        <v>44.2947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>588.0234</v>
+      </c>
+      <c r="D10" s="3">
+        <v>716.9713</v>
+      </c>
+      <c r="E10" s="3">
+        <v>128.9479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>853.6667</v>
+      </c>
+      <c r="D11" s="3">
+        <v>736.0561</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-117.6106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1152.1667</v>
+      </c>
+      <c r="D12" s="3">
+        <v>572.8255</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-579.3412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>707.6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>450.4025</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-257.1975</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>968</v>
+      </c>
+      <c r="D14" s="3">
+        <v>356.2455</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-611.7545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>823</v>
+      </c>
+      <c r="D15" s="3">
+        <v>285.6278</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-537.3722</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>762.5</v>
+      </c>
+      <c r="D16" s="3">
+        <v>394.57</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-367.93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1096</v>
+      </c>
+      <c r="D17" s="3">
+        <v>521.7147</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-574.2853</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="D18" s="3">
+        <v>548.401</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-551.599</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>869.5</v>
+      </c>
+      <c r="D19" s="3">
+        <v>623.1257000000001</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-246.3743</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>593.5333000000001</v>
+      </c>
+      <c r="D20" s="3">
+        <v>627.2762</v>
+      </c>
+      <c r="E20" s="3">
+        <v>33.7429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>683</v>
+      </c>
+      <c r="D21" s="3">
+        <v>686.2145</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.2145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>724.6667</v>
+      </c>
+      <c r="D22" s="3">
+        <v>804.151</v>
+      </c>
+      <c r="E22" s="3">
+        <v>79.4843</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>819.8645</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>910.3016</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>899.4774</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>970.0113</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>944.2597</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1003.598</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>969.4497</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1022.4906</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>983.6191</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>8.153</v>
-      </c>
-      <c r="E4">
-        <v>1.6115</v>
-      </c>
-      <c r="F4">
-        <v>1.665</v>
-      </c>
-      <c r="G4">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5">
-        <v>1687.4015</v>
-      </c>
-      <c r="E5">
-        <v>88.96429999999999</v>
-      </c>
-      <c r="F5">
-        <v>101.469</v>
-      </c>
-      <c r="G5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>163484.85</v>
-      </c>
-      <c r="E6">
-        <v>8535.122499999999</v>
-      </c>
-      <c r="F6">
-        <v>9731.2294</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7">
-        <v>1.1975</v>
-      </c>
-      <c r="E7">
-        <v>0.9651999999999999</v>
-      </c>
-      <c r="F7">
-        <v>1.0018</v>
-      </c>
-      <c r="G7">
-        <v>19</v>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>2016</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>196.6667</v>
+      </c>
+      <c r="D4" s="3">
+        <v>232.5953</v>
+      </c>
+      <c r="E4" s="3">
+        <v>35.9286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2016.5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>111</v>
+      </c>
+      <c r="D5" s="3">
+        <v>289.7322</v>
+      </c>
+      <c r="E5" s="3">
+        <v>178.7322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>187.1667</v>
+      </c>
+      <c r="D6" s="3">
+        <v>291.2325</v>
+      </c>
+      <c r="E6" s="3">
+        <v>104.0658</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>2017.5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3">
+        <v>174.3333</v>
+      </c>
+      <c r="D7" s="3">
+        <v>317.9104</v>
+      </c>
+      <c r="E7" s="3">
+        <v>143.5771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>2018</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>249.4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>297.6145</v>
+      </c>
+      <c r="E8" s="3">
+        <v>48.2145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>2018.5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3">
+        <v>276</v>
+      </c>
+      <c r="D9" s="3">
+        <v>301.9087</v>
+      </c>
+      <c r="E9" s="3">
+        <v>25.9087</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>226.75</v>
+      </c>
+      <c r="D10" s="3">
+        <v>286.2908</v>
+      </c>
+      <c r="E10" s="3">
+        <v>59.5408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>2019.5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3">
+        <v>335</v>
+      </c>
+      <c r="D11" s="3">
+        <v>294.0935</v>
+      </c>
+      <c r="E11" s="3">
+        <v>-40.9065</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>450.8333</v>
+      </c>
+      <c r="D12" s="3">
+        <v>232.3311</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-218.5022</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>2020.5</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3">
+        <v>270</v>
+      </c>
+      <c r="D13" s="3">
+        <v>186.0092</v>
+      </c>
+      <c r="E13" s="3">
+        <v>-83.99079999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>360.75</v>
+      </c>
+      <c r="D14" s="3">
+        <v>149.9273</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-210.8227</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>2021.5</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>384.75</v>
+      </c>
+      <c r="D15" s="3">
+        <v>122.8658</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-261.8842</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>320</v>
+      </c>
+      <c r="D16" s="3">
+        <v>163.7599</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-156.2401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>2022.5</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>354</v>
+      </c>
+      <c r="D17" s="3">
+        <v>212.3196</v>
+      </c>
+      <c r="E17" s="3">
+        <v>-141.6804</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3">
+        <v>398.3333</v>
+      </c>
+      <c r="D18" s="3">
+        <v>222.4809</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-175.8524</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>2023.5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3">
+        <v>310.6667</v>
+      </c>
+      <c r="D19" s="3">
+        <v>251.3645</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-59.3022</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3">
+        <v>345</v>
+      </c>
+      <c r="D20" s="3">
+        <v>252.0869</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-92.9131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>2024.5</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3">
+        <v>251.25</v>
+      </c>
+      <c r="D21" s="3">
+        <v>273.8032</v>
+      </c>
+      <c r="E21" s="3">
+        <v>22.5532</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3">
+        <v>270</v>
+      </c>
+      <c r="D22" s="3">
+        <v>321.2218</v>
+      </c>
+      <c r="E22" s="3">
+        <v>51.2218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>327.0328</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>2026.5</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3">
+        <v>361.4433</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>2027</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>357.1989</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>2027.5</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>384.0679</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>2028</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
+        <v>374.1673</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>2028.5</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>396.7942</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>2029</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
+        <v>383.7121</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>2029.5</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>403.9527</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>2030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>389.081</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/method1_results.xlsx
+++ b/method1_results.xlsx
@@ -572,10 +572,10 @@
         <v>2.14</v>
       </c>
       <c r="D4" s="3">
-        <v>2.9316</v>
+        <v>4.3564</v>
       </c>
       <c r="E4" s="3">
-        <v>0.7916</v>
+        <v>2.2164</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -589,10 +589,10 @@
         <v>3.024</v>
       </c>
       <c r="D5" s="3">
-        <v>3.5903</v>
+        <v>5.2035</v>
       </c>
       <c r="E5" s="3">
-        <v>0.5663</v>
+        <v>2.1795</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -606,10 +606,10 @@
         <v>2.8667</v>
       </c>
       <c r="D6" s="3">
-        <v>3.7874</v>
+        <v>4.6261</v>
       </c>
       <c r="E6" s="3">
-        <v>0.9207</v>
+        <v>1.7594</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -623,10 +623,10 @@
         <v>2.46</v>
       </c>
       <c r="D7" s="3">
-        <v>3.9903</v>
+        <v>4.607</v>
       </c>
       <c r="E7" s="3">
-        <v>1.5303</v>
+        <v>2.147</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -640,10 +640,10 @@
         <v>1.924</v>
       </c>
       <c r="D8" s="3">
-        <v>4.5543</v>
+        <v>5.7547</v>
       </c>
       <c r="E8" s="3">
-        <v>2.6303</v>
+        <v>3.8307</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -657,10 +657,10 @@
         <v>2.3333</v>
       </c>
       <c r="D9" s="3">
-        <v>5.0194</v>
+        <v>6.2168</v>
       </c>
       <c r="E9" s="3">
-        <v>2.6861</v>
+        <v>3.8835</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -674,10 +674,10 @@
         <v>3.1575</v>
       </c>
       <c r="D10" s="3">
-        <v>5.1173</v>
+        <v>5.6526</v>
       </c>
       <c r="E10" s="3">
-        <v>1.9598</v>
+        <v>2.4951</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -691,10 +691,10 @@
         <v>2.625</v>
       </c>
       <c r="D11" s="3">
-        <v>5.2327</v>
+        <v>5.601</v>
       </c>
       <c r="E11" s="3">
-        <v>2.6077</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -708,10 +708,10 @@
         <v>1.9733</v>
       </c>
       <c r="D12" s="3">
-        <v>5.4164</v>
+        <v>5.8577</v>
       </c>
       <c r="E12" s="3">
-        <v>3.4431</v>
+        <v>3.8844</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -725,10 +725,10 @@
         <v>2.308</v>
       </c>
       <c r="D13" s="3">
-        <v>5.5543</v>
+        <v>5.9347</v>
       </c>
       <c r="E13" s="3">
-        <v>3.2463</v>
+        <v>3.6267</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -742,10 +742,10 @@
         <v>1.9525</v>
       </c>
       <c r="D14" s="3">
-        <v>4.9556</v>
+        <v>3.9921</v>
       </c>
       <c r="E14" s="3">
-        <v>3.0031</v>
+        <v>2.0396</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -759,10 +759,10 @@
         <v>1.8125</v>
       </c>
       <c r="D15" s="3">
-        <v>4.5066</v>
+        <v>3.4094</v>
       </c>
       <c r="E15" s="3">
-        <v>2.6941</v>
+        <v>1.5969</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -776,10 +776,10 @@
         <v>2.46</v>
       </c>
       <c r="D16" s="3">
-        <v>5.0648</v>
+        <v>5.7405</v>
       </c>
       <c r="E16" s="3">
-        <v>2.6048</v>
+        <v>3.2805</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -793,10 +793,10 @@
         <v>1.7267</v>
       </c>
       <c r="D17" s="3">
-        <v>5.5352</v>
+        <v>6.5844</v>
       </c>
       <c r="E17" s="3">
-        <v>3.8085</v>
+        <v>4.8577</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -810,10 +810,10 @@
         <v>1.7667</v>
       </c>
       <c r="D18" s="3">
-        <v>5.5504</v>
+        <v>5.8927</v>
       </c>
       <c r="E18" s="3">
-        <v>3.7837</v>
+        <v>4.126</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -827,10 +827,10 @@
         <v>1.8217</v>
       </c>
       <c r="D19" s="3">
-        <v>5.6166</v>
+        <v>5.8383</v>
       </c>
       <c r="E19" s="3">
-        <v>3.7949</v>
+        <v>4.0166</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -844,10 +844,10 @@
         <v>2.09</v>
       </c>
       <c r="D20" s="3">
-        <v>5.2034</v>
+        <v>4.5262</v>
       </c>
       <c r="E20" s="3">
-        <v>3.1134</v>
+        <v>2.4362</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -861,10 +861,10 @@
         <v>2.1525</v>
       </c>
       <c r="D21" s="3">
-        <v>4.9353</v>
+        <v>4.2495</v>
       </c>
       <c r="E21" s="3">
-        <v>2.7828</v>
+        <v>2.097</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -878,10 +878,10 @@
         <v>1.99</v>
       </c>
       <c r="D22" s="3">
-        <v>4.6255</v>
+        <v>3.8621</v>
       </c>
       <c r="E22" s="3">
-        <v>2.6355</v>
+        <v>1.8721</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -895,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>4.7787</v>
+        <v>4.8255</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -912,7 +912,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>4.9584</v>
+        <v>5.2958</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>5.0284</v>
+        <v>5.2556</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -946,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>5.1456</v>
+        <v>5.4248</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -963,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>5.1688</v>
+        <v>5.2943</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -980,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>5.2509</v>
+        <v>5.4364</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -997,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>5.2478</v>
+        <v>5.2978</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -1014,7 +1014,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>5.3102</v>
+        <v>5.4375</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -1031,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>5.2922</v>
+        <v>5.2981</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -1083,10 +1083,10 @@
         <v>10.5967</v>
       </c>
       <c r="D4" s="3">
-        <v>10.0272</v>
+        <v>9.0021</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.5695</v>
+        <v>-1.5946</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1100,10 +1100,10 @@
         <v>3.628</v>
       </c>
       <c r="D5" s="3">
-        <v>10.2954</v>
+        <v>10.4705</v>
       </c>
       <c r="E5" s="3">
-        <v>6.6674</v>
+        <v>6.8425</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1117,10 +1117,10 @@
         <v>8.9633</v>
       </c>
       <c r="D6" s="3">
-        <v>9.4741</v>
+        <v>8.048299999999999</v>
       </c>
       <c r="E6" s="3">
-        <v>0.5108</v>
+        <v>-0.915</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1134,10 +1134,10 @@
         <v>5.1267</v>
       </c>
       <c r="D7" s="3">
-        <v>9.4466</v>
+        <v>8.9694</v>
       </c>
       <c r="E7" s="3">
-        <v>4.3199</v>
+        <v>3.8427</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1151,10 +1151,10 @@
         <v>10.686</v>
       </c>
       <c r="D8" s="3">
-        <v>8.461600000000001</v>
+        <v>6.5455</v>
       </c>
       <c r="E8" s="3">
-        <v>-2.2244</v>
+        <v>-4.1405</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1168,10 +1168,10 @@
         <v>6.5067</v>
       </c>
       <c r="D9" s="3">
-        <v>8.1723</v>
+        <v>7.0768</v>
       </c>
       <c r="E9" s="3">
-        <v>1.6656</v>
+        <v>0.5701000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1185,10 +1185,10 @@
         <v>5.988</v>
       </c>
       <c r="D10" s="3">
-        <v>7.4767</v>
+        <v>5.8958</v>
       </c>
       <c r="E10" s="3">
-        <v>1.4887</v>
+        <v>-0.0922</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1202,10 +1202,10 @@
         <v>5.3967</v>
       </c>
       <c r="D11" s="3">
-        <v>7.4044</v>
+        <v>6.8001</v>
       </c>
       <c r="E11" s="3">
-        <v>2.0077</v>
+        <v>1.4034</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1219,10 +1219,10 @@
         <v>9.0083</v>
       </c>
       <c r="D12" s="3">
-        <v>5.8143</v>
+        <v>2.7707</v>
       </c>
       <c r="E12" s="3">
-        <v>-3.194</v>
+        <v>-6.2376</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1236,10 +1236,10 @@
         <v>4.98</v>
       </c>
       <c r="D13" s="3">
-        <v>4.6217</v>
+        <v>1.5619</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.3583</v>
+        <v>-3.4181</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1253,10 +1253,10 @@
         <v>7.145</v>
       </c>
       <c r="D14" s="3">
-        <v>3.648</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="E14" s="3">
-        <v>-3.497</v>
+        <v>-6.1677</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1270,10 +1270,10 @@
         <v>4.2125</v>
       </c>
       <c r="D15" s="3">
-        <v>2.9177</v>
+        <v>0.802</v>
       </c>
       <c r="E15" s="3">
-        <v>-1.2948</v>
+        <v>-3.4105</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1287,10 +1287,10 @@
         <v>4.34</v>
       </c>
       <c r="D16" s="3">
-        <v>3.81</v>
+        <v>4.7816</v>
       </c>
       <c r="E16" s="3">
-        <v>-0.53</v>
+        <v>0.4416</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1304,10 +1304,10 @@
         <v>5.17</v>
       </c>
       <c r="D17" s="3">
-        <v>4.8507</v>
+        <v>7.0154</v>
       </c>
       <c r="E17" s="3">
-        <v>-0.3193</v>
+        <v>1.8454</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1321,10 +1321,10 @@
         <v>9.01</v>
       </c>
       <c r="D18" s="3">
-        <v>5.0478</v>
+        <v>6.052</v>
       </c>
       <c r="E18" s="3">
-        <v>-3.9622</v>
+        <v>-2.958</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1338,10 +1338,10 @@
         <v>4.0483</v>
       </c>
       <c r="D19" s="3">
-        <v>5.6577</v>
+        <v>7.0568</v>
       </c>
       <c r="E19" s="3">
-        <v>1.6094</v>
+        <v>3.0085</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1355,10 +1355,10 @@
         <v>5.25</v>
       </c>
       <c r="D20" s="3">
-        <v>5.6762</v>
+        <v>6.1291</v>
       </c>
       <c r="E20" s="3">
-        <v>0.4262</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1372,10 +1372,10 @@
         <v>3.335</v>
       </c>
       <c r="D21" s="3">
-        <v>6.1897</v>
+        <v>7.2498</v>
       </c>
       <c r="E21" s="3">
-        <v>2.8547</v>
+        <v>3.9148</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1572,10 +1572,10 @@
         <v>0.383</v>
       </c>
       <c r="D4" s="3">
-        <v>1.8089</v>
+        <v>0.18</v>
       </c>
       <c r="E4" s="3">
-        <v>1.4259</v>
+        <v>-0.203</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1589,10 +1589,10 @@
         <v>0.314</v>
       </c>
       <c r="D5" s="3">
-        <v>3.4778</v>
+        <v>0.119</v>
       </c>
       <c r="E5" s="3">
-        <v>3.1638</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1606,10 +1606,10 @@
         <v>0.3912</v>
       </c>
       <c r="D6" s="3">
-        <v>3.9008</v>
+        <v>0.1033</v>
       </c>
       <c r="E6" s="3">
-        <v>3.5096</v>
+        <v>-0.2879</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1623,10 +1623,10 @@
         <v>0.3427</v>
       </c>
       <c r="D7" s="3">
-        <v>4.7253</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="E7" s="3">
-        <v>4.3826</v>
+        <v>-0.2441</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1640,10 +1640,10 @@
         <v>0.4622</v>
       </c>
       <c r="D8" s="3">
-        <v>4.5374</v>
+        <v>0.099</v>
       </c>
       <c r="E8" s="3">
-        <v>4.0752</v>
+        <v>-0.3632</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1657,10 +1657,10 @@
         <v>0.395</v>
       </c>
       <c r="D9" s="3">
-        <v>4.784</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="E9" s="3">
-        <v>4.389</v>
+        <v>-0.2959</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1674,10 +1674,10 @@
         <v>0.218</v>
       </c>
       <c r="D10" s="3">
-        <v>4.5854</v>
+        <v>0.1104</v>
       </c>
       <c r="E10" s="3">
-        <v>4.3674</v>
+        <v>-0.1076</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1691,10 +1691,10 @@
         <v>0.466</v>
       </c>
       <c r="D11" s="3">
-        <v>4.824</v>
+        <v>0.1138</v>
       </c>
       <c r="E11" s="3">
-        <v>4.358</v>
+        <v>-0.3522</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1708,10 +1708,10 @@
         <v>0.3383</v>
       </c>
       <c r="D12" s="3">
-        <v>3.6439</v>
+        <v>0.1068</v>
       </c>
       <c r="E12" s="3">
-        <v>3.3056</v>
+        <v>-0.2315</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1725,10 +1725,10 @@
         <v>0.2672</v>
       </c>
       <c r="D13" s="3">
-        <v>2.7589</v>
+        <v>0.1047</v>
       </c>
       <c r="E13" s="3">
-        <v>2.4917</v>
+        <v>-0.1625</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1742,10 +1742,10 @@
         <v>0.379</v>
       </c>
       <c r="D14" s="3">
-        <v>2.0921</v>
+        <v>0.0956</v>
       </c>
       <c r="E14" s="3">
-        <v>1.7131</v>
+        <v>-0.2834</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1759,10 +1759,10 @@
         <v>0.3395</v>
       </c>
       <c r="D15" s="3">
-        <v>1.592</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E15" s="3">
-        <v>1.2525</v>
+        <v>-0.2467</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1776,10 +1776,10 @@
         <v>0.2415</v>
       </c>
       <c r="D16" s="3">
-        <v>2.4179</v>
+        <v>0.1247</v>
       </c>
       <c r="E16" s="3">
-        <v>2.1764</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1793,10 +1793,10 @@
         <v>0.296</v>
       </c>
       <c r="D17" s="3">
-        <v>3.5131</v>
+        <v>0.1343</v>
       </c>
       <c r="E17" s="3">
-        <v>3.2171</v>
+        <v>-0.1617</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1810,10 +1810,10 @@
         <v>0.3203</v>
       </c>
       <c r="D18" s="3">
-        <v>3.8662</v>
+        <v>0.1145</v>
       </c>
       <c r="E18" s="3">
-        <v>3.5459</v>
+        <v>-0.2058</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1827,10 +1827,10 @@
         <v>0.313</v>
       </c>
       <c r="D19" s="3">
-        <v>4.635</v>
+        <v>0.1086</v>
       </c>
       <c r="E19" s="3">
-        <v>4.322</v>
+        <v>-0.2044</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1844,10 +1844,10 @@
         <v>0.25</v>
       </c>
       <c r="D20" s="3">
-        <v>4.4689</v>
+        <v>0.1185</v>
       </c>
       <c r="E20" s="3">
-        <v>4.2189</v>
+        <v>-0.1315</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1861,10 +1861,10 @@
         <v>0.3063</v>
       </c>
       <c r="D21" s="3">
-        <v>4.7291</v>
+        <v>0.1215</v>
       </c>
       <c r="E21" s="3">
-        <v>4.4228</v>
+        <v>-0.1848</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1878,10 +1878,10 @@
         <v>0.1853</v>
       </c>
       <c r="D22" s="3">
-        <v>5.6066</v>
+        <v>0.1217</v>
       </c>
       <c r="E22" s="3">
-        <v>5.4213</v>
+        <v>-0.0636</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1895,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>5.7236</v>
+        <v>0.1124</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -1912,7 +1912,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>6.408</v>
+        <v>0.1096</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -1929,7 +1929,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>6.3247</v>
+        <v>0.1088</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -1946,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>6.8589</v>
+        <v>0.1085</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -1963,7 +1963,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>6.6629</v>
+        <v>0.1084</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -1980,7 +1980,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>7.1125</v>
+        <v>0.1084</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -1997,7 +1997,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>6.8531</v>
+        <v>0.1084</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>7.2551</v>
+        <v>0.1084</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -2031,7 +2031,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>6.96</v>
+        <v>0.1084</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -2083,10 +2083,10 @@
         <v>0.0489</v>
       </c>
       <c r="D4" s="3">
-        <v>0.0635</v>
+        <v>0.0351</v>
       </c>
       <c r="E4" s="3">
-        <v>0.0146</v>
+        <v>-0.0138</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2100,10 +2100,10 @@
         <v>0.0542</v>
       </c>
       <c r="D5" s="3">
-        <v>0.0823</v>
+        <v>0.031</v>
       </c>
       <c r="E5" s="3">
-        <v>0.0281</v>
+        <v>-0.0232</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2117,10 +2117,10 @@
         <v>0.1239</v>
       </c>
       <c r="D6" s="3">
-        <v>0.0852</v>
+        <v>0.0287</v>
       </c>
       <c r="E6" s="3">
-        <v>-0.0387</v>
+        <v>-0.0951</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2134,10 +2134,10 @@
         <v>0.04</v>
       </c>
       <c r="D7" s="3">
-        <v>0.094</v>
+        <v>0.028</v>
       </c>
       <c r="E7" s="3">
-        <v>0.054</v>
+        <v>-0.012</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2151,10 +2151,10 @@
         <v>0.0825</v>
       </c>
       <c r="D8" s="3">
-        <v>0.0882</v>
+        <v>0.0228</v>
       </c>
       <c r="E8" s="3">
-        <v>0.0057</v>
+        <v>-0.0597</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2168,10 +2168,10 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="D9" s="3">
-        <v>0.089</v>
+        <v>0.0212</v>
       </c>
       <c r="E9" s="3">
-        <v>-0.0072</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2185,10 +2185,10 @@
         <v>0.0511</v>
       </c>
       <c r="D10" s="3">
-        <v>0.0843</v>
+        <v>0.0202</v>
       </c>
       <c r="E10" s="3">
-        <v>0.0332</v>
+        <v>-0.0309</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2202,10 +2202,10 @@
         <v>0.089</v>
       </c>
       <c r="D11" s="3">
-        <v>0.0859</v>
+        <v>0.0199</v>
       </c>
       <c r="E11" s="3">
-        <v>-0.0031</v>
+        <v>-0.06909999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2219,10 +2219,10 @@
         <v>0.0876</v>
       </c>
       <c r="D12" s="3">
-        <v>0.0713</v>
+        <v>0.0254</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.0163</v>
+        <v>-0.0622</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2236,10 +2236,10 @@
         <v>0.0726</v>
       </c>
       <c r="D13" s="3">
-        <v>0.0604</v>
+        <v>0.027</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.0122</v>
+        <v>-0.0456</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2253,10 +2253,10 @@
         <v>0.06859999999999999</v>
       </c>
       <c r="D14" s="3">
-        <v>0.0502</v>
+        <v>0.0217</v>
       </c>
       <c r="E14" s="3">
-        <v>-0.0184</v>
+        <v>-0.0469</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2270,10 +2270,10 @@
         <v>0.0761</v>
       </c>
       <c r="D15" s="3">
-        <v>0.0425</v>
+        <v>0.0201</v>
       </c>
       <c r="E15" s="3">
-        <v>-0.0336</v>
+        <v>-0.056</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2287,10 +2287,10 @@
         <v>0.0574</v>
       </c>
       <c r="D16" s="3">
-        <v>0.0559</v>
+        <v>0.03</v>
       </c>
       <c r="E16" s="3">
-        <v>-0.0015</v>
+        <v>-0.0274</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2304,10 +2304,10 @@
         <v>0.0403</v>
       </c>
       <c r="D17" s="3">
-        <v>0.0722</v>
+        <v>0.0329</v>
       </c>
       <c r="E17" s="3">
-        <v>0.0319</v>
+        <v>-0.0074</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2321,10 +2321,10 @@
         <v>0.0573</v>
       </c>
       <c r="D18" s="3">
-        <v>0.076</v>
+        <v>0.0271</v>
       </c>
       <c r="E18" s="3">
-        <v>0.0187</v>
+        <v>-0.0302</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2338,10 +2338,10 @@
         <v>0.0626</v>
       </c>
       <c r="D19" s="3">
-        <v>0.0854</v>
+        <v>0.0253</v>
       </c>
       <c r="E19" s="3">
-        <v>0.0228</v>
+        <v>-0.0373</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2355,10 +2355,10 @@
         <v>0.0621</v>
       </c>
       <c r="D20" s="3">
-        <v>0.0824</v>
+        <v>0.0239</v>
       </c>
       <c r="E20" s="3">
-        <v>0.0204</v>
+        <v>-0.0382</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2372,10 +2372,10 @@
         <v>0.0464</v>
       </c>
       <c r="D21" s="3">
-        <v>0.0852</v>
+        <v>0.0235</v>
       </c>
       <c r="E21" s="3">
-        <v>0.0388</v>
+        <v>-0.0229</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2389,10 +2389,10 @@
         <v>0.037</v>
       </c>
       <c r="D22" s="3">
-        <v>0.0961</v>
+        <v>0.023</v>
       </c>
       <c r="E22" s="3">
-        <v>0.0591</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2406,7 +2406,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>0.0977</v>
+        <v>0.0243</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -2423,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>0.1067</v>
+        <v>0.0246</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -2440,7 +2440,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>0.1057</v>
+        <v>0.0247</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -2457,7 +2457,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>0.1127</v>
+        <v>0.0248</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -2474,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>0.1102</v>
+        <v>0.0248</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -2491,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>0.116</v>
+        <v>0.0248</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -2508,7 +2508,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>0.1127</v>
+        <v>0.0248</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -2525,7 +2525,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>0.1179</v>
+        <v>0.0248</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -2542,7 +2542,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>0.1141</v>
+        <v>0.0248</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -2603,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2.5581</v>
+        <v>2.9117</v>
       </c>
       <c r="F4">
-        <v>2.7335</v>
+        <v>3.0652</v>
       </c>
       <c r="G4">
         <v>19</v>
@@ -2626,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.1262</v>
+        <v>0.1467</v>
       </c>
       <c r="F5">
-        <v>0.1452</v>
+        <v>0.1767</v>
       </c>
       <c r="G5">
         <v>19</v>
@@ -2649,10 +2649,10 @@
         <v>285.4063</v>
       </c>
       <c r="E6">
-        <v>48.5367</v>
+        <v>76.59059999999999</v>
       </c>
       <c r="F6">
-        <v>57.2457</v>
+        <v>87.0596</v>
       </c>
       <c r="G6">
         <v>19</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.4808</v>
+        <v>0.5309</v>
       </c>
       <c r="F7">
-        <v>0.5582</v>
+        <v>0.6017</v>
       </c>
       <c r="G7">
         <v>19</v>
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3.7708</v>
+        <v>4.4064</v>
       </c>
       <c r="F8">
-        <v>3.9845</v>
+        <v>4.6118</v>
       </c>
       <c r="G8">
         <v>19</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.1824</v>
+        <v>0.1864</v>
       </c>
       <c r="F9">
-        <v>0.2062</v>
+        <v>0.2115</v>
       </c>
       <c r="G9">
         <v>19</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>3.5569</v>
+        <v>4.4076</v>
       </c>
       <c r="F10">
-        <v>4.3939</v>
+        <v>6.1055</v>
       </c>
       <c r="G10">
         <v>19</v>
@@ -2764,10 +2764,10 @@
         <v>1653.9055</v>
       </c>
       <c r="E11">
-        <v>286.5115</v>
+        <v>358.8993</v>
       </c>
       <c r="F11">
-        <v>352.0667</v>
+        <v>452.7928</v>
       </c>
       <c r="G11">
         <v>19</v>
@@ -2787,10 +2787,10 @@
         <v>581.4258</v>
       </c>
       <c r="E12">
-        <v>111.1493</v>
+        <v>138.0101</v>
       </c>
       <c r="F12">
-        <v>132.071</v>
+        <v>175.9121</v>
       </c>
       <c r="G12">
         <v>19</v>
@@ -2821,16 +2821,16 @@
         <v>41</v>
       </c>
       <c r="C14">
-        <v>0.012511111</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>3.461</v>
+        <v>0.2127</v>
       </c>
       <c r="F14">
-        <v>3.6436</v>
+        <v>0.2268</v>
       </c>
       <c r="G14">
         <v>19</v>
@@ -2844,16 +2844,16 @@
         <v>41</v>
       </c>
       <c r="C15">
-        <v>0.000163111</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.0241</v>
+        <v>0.0404</v>
       </c>
       <c r="F15">
-        <v>0.0288</v>
+        <v>0.0467</v>
       </c>
       <c r="G15">
         <v>19</v>
@@ -2905,10 +2905,10 @@
         <v>0.1792</v>
       </c>
       <c r="D4" s="3">
-        <v>0.1624</v>
+        <v>0.1321</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.0168</v>
+        <v>-0.0471</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2922,10 +2922,10 @@
         <v>0.0291</v>
       </c>
       <c r="D5" s="3">
-        <v>0.1497</v>
+        <v>0.118</v>
       </c>
       <c r="E5" s="3">
-        <v>0.1206</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2939,10 +2939,10 @@
         <v>0.1017</v>
       </c>
       <c r="D6" s="3">
-        <v>0.1345</v>
+        <v>0.0974</v>
       </c>
       <c r="E6" s="3">
-        <v>0.0328</v>
+        <v>-0.0043</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2956,10 +2956,10 @@
         <v>0.0218</v>
       </c>
       <c r="D7" s="3">
-        <v>0.123</v>
+        <v>0.0912</v>
       </c>
       <c r="E7" s="3">
-        <v>0.1012</v>
+        <v>0.0694</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2973,10 +2973,10 @@
         <v>0.1515</v>
       </c>
       <c r="D8" s="3">
-        <v>0.1125</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E8" s="3">
-        <v>-0.039</v>
+        <v>-0.0675</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2990,10 +2990,10 @@
         <v>0.0113</v>
       </c>
       <c r="D9" s="3">
-        <v>0.1046</v>
+        <v>0.0818</v>
       </c>
       <c r="E9" s="3">
-        <v>0.09329999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3007,10 +3007,10 @@
         <v>0.0765</v>
       </c>
       <c r="D10" s="3">
-        <v>0.1241</v>
+        <v>0.1525</v>
       </c>
       <c r="E10" s="3">
-        <v>0.0476</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3024,10 +3024,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" s="3">
-        <v>0.1388</v>
+        <v>0.1737</v>
       </c>
       <c r="E11" s="3">
-        <v>0.1048</v>
+        <v>0.1397</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3041,10 +3041,10 @@
         <v>0.0917</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1784</v>
+        <v>0.2602</v>
       </c>
       <c r="E12" s="3">
-        <v>0.0867</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3058,10 +3058,10 @@
         <v>0.0177</v>
       </c>
       <c r="D13" s="3">
-        <v>0.2082</v>
+        <v>0.2862</v>
       </c>
       <c r="E13" s="3">
-        <v>0.1905</v>
+        <v>0.2685</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3075,10 +3075,10 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="D14" s="3">
-        <v>0.1885</v>
+        <v>0.1765</v>
       </c>
       <c r="E14" s="3">
-        <v>0.1108</v>
+        <v>0.0987</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3092,10 +3092,10 @@
         <v>0.037</v>
       </c>
       <c r="D15" s="3">
-        <v>0.1737</v>
+        <v>0.1436</v>
       </c>
       <c r="E15" s="3">
-        <v>0.1367</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3109,10 +3109,10 @@
         <v>0.11</v>
       </c>
       <c r="D16" s="3">
-        <v>0.1712</v>
+        <v>0.1575</v>
       </c>
       <c r="E16" s="3">
-        <v>0.0612</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3126,10 +3126,10 @@
         <v>0.0092</v>
       </c>
       <c r="D17" s="3">
-        <v>0.1692</v>
+        <v>0.1617</v>
       </c>
       <c r="E17" s="3">
-        <v>0.16</v>
+        <v>0.1525</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3143,10 +3143,10 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="D18" s="3">
-        <v>0.2338</v>
+        <v>0.3477</v>
       </c>
       <c r="E18" s="3">
-        <v>0.1565</v>
+        <v>0.2704</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3160,10 +3160,10 @@
         <v>0.0403</v>
       </c>
       <c r="D19" s="3">
-        <v>0.2822</v>
+        <v>0.4035</v>
       </c>
       <c r="E19" s="3">
-        <v>0.2419</v>
+        <v>0.3632</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3177,10 +3177,10 @@
         <v>0.0625</v>
       </c>
       <c r="D20" s="3">
-        <v>0.267</v>
+        <v>0.276</v>
       </c>
       <c r="E20" s="3">
-        <v>0.2045</v>
+        <v>0.2135</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3194,10 +3194,10 @@
         <v>0.012</v>
       </c>
       <c r="D21" s="3">
-        <v>0.2556</v>
+        <v>0.2378</v>
       </c>
       <c r="E21" s="3">
-        <v>0.2436</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3211,10 +3211,10 @@
         <v>0.0406</v>
       </c>
       <c r="D22" s="3">
-        <v>0.2908</v>
+        <v>0.3489</v>
       </c>
       <c r="E22" s="3">
-        <v>0.2502</v>
+        <v>0.3083</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3228,7 +3228,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>0.2703</v>
+        <v>0.2506</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -3245,7 +3245,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>0.2548</v>
+        <v>0.2212</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -3262,7 +3262,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>0.2433</v>
+        <v>0.2123</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -3279,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>0.2346</v>
+        <v>0.2097</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -3296,7 +3296,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>0.2281</v>
+        <v>0.2089</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -3313,7 +3313,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>0.2232</v>
+        <v>0.2086</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -3330,7 +3330,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>0.2195</v>
+        <v>0.2086</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -3347,7 +3347,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>0.2168</v>
+        <v>0.2085</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -3364,7 +3364,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>0.2147</v>
+        <v>0.2085</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -3416,10 +3416,10 @@
         <v>152.3333</v>
       </c>
       <c r="D4" s="3">
-        <v>165.1339</v>
+        <v>188.175</v>
       </c>
       <c r="E4" s="3">
-        <v>12.8006</v>
+        <v>35.8417</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3433,10 +3433,10 @@
         <v>87.98</v>
       </c>
       <c r="D5" s="3">
-        <v>193.619</v>
+        <v>251.8045</v>
       </c>
       <c r="E5" s="3">
-        <v>105.639</v>
+        <v>163.8245</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3450,10 +3450,10 @@
         <v>115.05</v>
       </c>
       <c r="D6" s="3">
-        <v>188.8659</v>
+        <v>197.766</v>
       </c>
       <c r="E6" s="3">
-        <v>73.8159</v>
+        <v>82.71599999999999</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3467,10 +3467,10 @@
         <v>104.1333</v>
       </c>
       <c r="D7" s="3">
-        <v>201.2847</v>
+        <v>226.3085</v>
       </c>
       <c r="E7" s="3">
-        <v>97.1514</v>
+        <v>122.1752</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3484,10 +3484,10 @@
         <v>139.4</v>
       </c>
       <c r="D8" s="3">
-        <v>185.3351</v>
+        <v>164.1331</v>
       </c>
       <c r="E8" s="3">
-        <v>45.9351</v>
+        <v>24.7331</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3501,10 +3501,10 @@
         <v>125.7667</v>
       </c>
       <c r="D9" s="3">
-        <v>185.5807</v>
+        <v>179.6621</v>
       </c>
       <c r="E9" s="3">
-        <v>59.814</v>
+        <v>53.8954</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3518,10 +3518,10 @@
         <v>98.61069999999999</v>
       </c>
       <c r="D10" s="3">
-        <v>174.2978</v>
+        <v>152.2129</v>
       </c>
       <c r="E10" s="3">
-        <v>75.687</v>
+        <v>53.6021</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3535,10 +3535,10 @@
         <v>130</v>
       </c>
       <c r="D11" s="3">
-        <v>178.0433</v>
+        <v>178.1598</v>
       </c>
       <c r="E11" s="3">
-        <v>48.0433</v>
+        <v>48.1598</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3552,10 +3552,10 @@
         <v>178.5</v>
       </c>
       <c r="D12" s="3">
-        <v>138.2425</v>
+        <v>66.6361</v>
       </c>
       <c r="E12" s="3">
-        <v>-40.2575</v>
+        <v>-111.8639</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3569,10 +3569,10 @@
         <v>112.66</v>
       </c>
       <c r="D13" s="3">
-        <v>108.392</v>
+        <v>33.1791</v>
       </c>
       <c r="E13" s="3">
-        <v>-4.268</v>
+        <v>-79.48090000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3586,10 +3586,10 @@
         <v>150.25</v>
       </c>
       <c r="D14" s="3">
-        <v>85.9472</v>
+        <v>22.9827</v>
       </c>
       <c r="E14" s="3">
-        <v>-64.3028</v>
+        <v>-127.2673</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3603,10 +3603,10 @@
         <v>112.25</v>
       </c>
       <c r="D15" s="3">
-        <v>69.11360000000001</v>
+        <v>19.9237</v>
       </c>
       <c r="E15" s="3">
-        <v>-43.1364</v>
+        <v>-92.3263</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3620,10 +3620,10 @@
         <v>105</v>
       </c>
       <c r="D16" s="3">
-        <v>94.93000000000001</v>
+        <v>126.6425</v>
       </c>
       <c r="E16" s="3">
-        <v>-10.07</v>
+        <v>21.6425</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3637,10 +3637,10 @@
         <v>129</v>
       </c>
       <c r="D17" s="3">
-        <v>126.3</v>
+        <v>192.2798</v>
       </c>
       <c r="E17" s="3">
-        <v>-2.7</v>
+        <v>63.2798</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3654,10 +3654,10 @@
         <v>151</v>
       </c>
       <c r="D18" s="3">
-        <v>133.4853</v>
+        <v>166.2128</v>
       </c>
       <c r="E18" s="3">
-        <v>-17.5147</v>
+        <v>15.2128</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3671,10 +3671,10 @@
         <v>122.3333</v>
       </c>
       <c r="D19" s="3">
-        <v>152.7299</v>
+        <v>197.1883</v>
       </c>
       <c r="E19" s="3">
-        <v>30.3966</v>
+        <v>74.855</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3688,10 +3688,10 @@
         <v>97.77500000000001</v>
       </c>
       <c r="D20" s="3">
-        <v>151.3113</v>
+        <v>162.0955</v>
       </c>
       <c r="E20" s="3">
-        <v>53.5363</v>
+        <v>64.3205</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3705,10 +3705,10 @@
         <v>118</v>
       </c>
       <c r="D21" s="3">
-        <v>163.2509</v>
+        <v>187.9775</v>
       </c>
       <c r="E21" s="3">
-        <v>45.2509</v>
+        <v>69.97750000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3722,10 +3722,10 @@
         <v>99.5667</v>
       </c>
       <c r="D22" s="3">
-        <v>191.4454</v>
+        <v>249.6134</v>
       </c>
       <c r="E22" s="3">
-        <v>91.87869999999999</v>
+        <v>150.0467</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3739,7 +3739,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>195.079</v>
+        <v>219.07</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -3756,7 +3756,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>216.6025</v>
+        <v>262.542</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -3773,7 +3773,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>213.9469</v>
+        <v>222.9486</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -3790,7 +3790,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>230.7534</v>
+        <v>263.7056</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -3807,7 +3807,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>224.56</v>
+        <v>223.2977</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -3824,7 +3824,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>238.7132</v>
+        <v>263.8103</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -3841,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>230.5299</v>
+        <v>223.3291</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -3858,7 +3858,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>243.1906</v>
+        <v>263.8197</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -3875,7 +3875,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>233.888</v>
+        <v>223.3319</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -3927,10 +3927,10 @@
         <v>1.111</v>
       </c>
       <c r="D4" s="3">
-        <v>0.9679</v>
+        <v>0.7103</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.1431</v>
+        <v>-0.4007</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3944,10 +3944,10 @@
         <v>0.6304</v>
       </c>
       <c r="D5" s="3">
-        <v>0.8908</v>
+        <v>0.6748</v>
       </c>
       <c r="E5" s="3">
-        <v>0.2604</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3961,10 +3961,10 @@
         <v>1.027</v>
       </c>
       <c r="D6" s="3">
-        <v>0.7915</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="E6" s="3">
-        <v>-0.2355</v>
+        <v>-0.4791</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3978,10 +3978,10 @@
         <v>0.8773</v>
       </c>
       <c r="D7" s="3">
-        <v>0.7426</v>
+        <v>0.5815</v>
       </c>
       <c r="E7" s="3">
-        <v>-0.1347</v>
+        <v>-0.2958</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3995,10 +3995,10 @@
         <v>1.0592</v>
       </c>
       <c r="D8" s="3">
-        <v>0.6585</v>
+        <v>0.4587</v>
       </c>
       <c r="E8" s="3">
-        <v>-0.4007</v>
+        <v>-0.6005</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4012,10 +4012,10 @@
         <v>0.632</v>
       </c>
       <c r="D9" s="3">
-        <v>0.6149</v>
+        <v>0.4767</v>
       </c>
       <c r="E9" s="3">
-        <v>-0.0171</v>
+        <v>-0.1553</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4029,10 +4029,10 @@
         <v>1.1803</v>
       </c>
       <c r="D10" s="3">
-        <v>0.6041</v>
+        <v>0.5431</v>
       </c>
       <c r="E10" s="3">
-        <v>-0.5762</v>
+        <v>-0.6371</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4046,10 +4046,10 @@
         <v>0.9045</v>
       </c>
       <c r="D11" s="3">
-        <v>0.6155</v>
+        <v>0.6177</v>
       </c>
       <c r="E11" s="3">
-        <v>-0.289</v>
+        <v>-0.2868</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4063,10 +4063,10 @@
         <v>1.4617</v>
       </c>
       <c r="D12" s="3">
-        <v>0.5683</v>
+        <v>0.4841</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.8934</v>
+        <v>-0.9776</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4080,10 +4080,10 @@
         <v>0.9718</v>
       </c>
       <c r="D13" s="3">
-        <v>0.533</v>
+        <v>0.4441</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.4388</v>
+        <v>-0.5276999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4097,10 +4097,10 @@
         <v>1.4625</v>
       </c>
       <c r="D14" s="3">
-        <v>0.4775</v>
+        <v>0.3509</v>
       </c>
       <c r="E14" s="3">
-        <v>-0.985</v>
+        <v>-1.1116</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4114,10 +4114,10 @@
         <v>0.9625</v>
       </c>
       <c r="D15" s="3">
-        <v>0.4358</v>
+        <v>0.3229</v>
       </c>
       <c r="E15" s="3">
-        <v>-0.5266999999999999</v>
+        <v>-0.6395999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4131,10 +4131,10 @@
         <v>1.395</v>
       </c>
       <c r="D16" s="3">
-        <v>0.4988</v>
+        <v>0.5782</v>
       </c>
       <c r="E16" s="3">
-        <v>-0.8962</v>
+        <v>-0.8168</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4148,10 +4148,10 @@
         <v>0.8877</v>
       </c>
       <c r="D17" s="3">
-        <v>0.57</v>
+        <v>0.722</v>
       </c>
       <c r="E17" s="3">
-        <v>-0.3177</v>
+        <v>-0.1657</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4165,10 +4165,10 @@
         <v>1.4013</v>
       </c>
       <c r="D18" s="3">
-        <v>0.5627</v>
+        <v>0.5952</v>
       </c>
       <c r="E18" s="3">
-        <v>-0.8386</v>
+        <v>-0.8061</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4182,10 +4182,10 @@
         <v>0.9702</v>
       </c>
       <c r="D19" s="3">
-        <v>0.5827</v>
+        <v>0.6283</v>
       </c>
       <c r="E19" s="3">
-        <v>-0.3875</v>
+        <v>-0.3419</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4199,10 +4199,10 @@
         <v>1.315</v>
       </c>
       <c r="D20" s="3">
-        <v>0.5449000000000001</v>
+        <v>0.4906</v>
       </c>
       <c r="E20" s="3">
-        <v>-0.7701</v>
+        <v>-0.8244</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4216,10 +4216,10 @@
         <v>0.8648</v>
       </c>
       <c r="D21" s="3">
-        <v>0.5359</v>
+        <v>0.5036</v>
       </c>
       <c r="E21" s="3">
-        <v>-0.3288</v>
+        <v>-0.3611</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4233,10 +4233,10 @@
         <v>1.2833</v>
       </c>
       <c r="D22" s="3">
-        <v>0.587</v>
+        <v>0.6692</v>
       </c>
       <c r="E22" s="3">
-        <v>-0.6963</v>
+        <v>-0.6141</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4250,7 +4250,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>0.5927</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -4267,7 +4267,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>0.627</v>
+        <v>0.6993</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -4284,7 +4284,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>0.6227</v>
+        <v>0.6365</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -4301,7 +4301,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>0.6495</v>
+        <v>0.702</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -4318,7 +4318,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>0.6395</v>
+        <v>0.6373</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -4335,7 +4335,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>0.6622</v>
+        <v>0.7022</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -4352,7 +4352,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>0.649</v>
+        <v>0.6374</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -4369,7 +4369,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>0.6693</v>
+        <v>0.7023</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -4386,7 +4386,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>0.6544</v>
+        <v>0.6374</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -4438,10 +4438,10 @@
         <v>1.9397</v>
       </c>
       <c r="D4" s="3">
-        <v>3.3374</v>
+        <v>5.8533</v>
       </c>
       <c r="E4" s="3">
-        <v>1.3977</v>
+        <v>3.9136</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4455,10 +4455,10 @@
         <v>2.1848</v>
       </c>
       <c r="D5" s="3">
-        <v>4.6399</v>
+        <v>7.7393</v>
       </c>
       <c r="E5" s="3">
-        <v>2.4551</v>
+        <v>5.5545</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4472,10 +4472,10 @@
         <v>1.6683</v>
       </c>
       <c r="D6" s="3">
-        <v>5.3441</v>
+        <v>7.5415</v>
       </c>
       <c r="E6" s="3">
-        <v>3.6758</v>
+        <v>5.8732</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4489,10 +4489,10 @@
         <v>2.0067</v>
       </c>
       <c r="D7" s="3">
-        <v>6.0875</v>
+        <v>8.0847</v>
       </c>
       <c r="E7" s="3">
-        <v>4.0808</v>
+        <v>6.078</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4506,10 +4506,10 @@
         <v>4.674</v>
       </c>
       <c r="D8" s="3">
-        <v>6.4764</v>
+        <v>7.7755</v>
       </c>
       <c r="E8" s="3">
-        <v>1.8024</v>
+        <v>3.1015</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4523,10 +4523,10 @@
         <v>2.44</v>
       </c>
       <c r="D9" s="3">
-        <v>6.9324</v>
+        <v>8.142899999999999</v>
       </c>
       <c r="E9" s="3">
-        <v>4.4924</v>
+        <v>5.7029</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4540,10 +4540,10 @@
         <v>12.4875</v>
       </c>
       <c r="D10" s="3">
-        <v>6.9366</v>
+        <v>7.3075</v>
       </c>
       <c r="E10" s="3">
-        <v>-5.5509</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4557,10 +4557,10 @@
         <v>3.695</v>
       </c>
       <c r="D11" s="3">
-        <v>7.1042</v>
+        <v>7.517</v>
       </c>
       <c r="E11" s="3">
-        <v>3.4092</v>
+        <v>3.822</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4574,10 +4574,10 @@
         <v>7.4933</v>
       </c>
       <c r="D12" s="3">
-        <v>6.5689</v>
+        <v>5.7292</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.9244</v>
+        <v>-1.7641</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4591,10 +4591,10 @@
         <v>2.326</v>
       </c>
       <c r="D13" s="3">
-        <v>6.1674</v>
+        <v>5.1929</v>
       </c>
       <c r="E13" s="3">
-        <v>3.8414</v>
+        <v>2.8669</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4608,10 +4608,10 @@
         <v>1.6138</v>
       </c>
       <c r="D14" s="3">
-        <v>5.573</v>
+        <v>4.2108</v>
       </c>
       <c r="E14" s="3">
-        <v>3.9593</v>
+        <v>2.597</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4625,10 +4625,10 @@
         <v>0.8695000000000001</v>
       </c>
       <c r="D15" s="3">
-        <v>5.1272</v>
+        <v>3.9161</v>
       </c>
       <c r="E15" s="3">
-        <v>4.2577</v>
+        <v>3.0466</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4642,10 +4642,10 @@
         <v>1.1195</v>
       </c>
       <c r="D16" s="3">
-        <v>5.4032</v>
+        <v>5.5366</v>
       </c>
       <c r="E16" s="3">
-        <v>4.2837</v>
+        <v>4.4171</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4659,10 +4659,10 @@
         <v>0.1493</v>
       </c>
       <c r="D17" s="3">
-        <v>5.8119</v>
+        <v>6.5877</v>
       </c>
       <c r="E17" s="3">
-        <v>5.6626</v>
+        <v>6.4384</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4676,10 +4676,10 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="D18" s="3">
-        <v>5.8538</v>
+        <v>6.1619</v>
       </c>
       <c r="E18" s="3">
-        <v>5.1708</v>
+        <v>5.4789</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4693,10 +4693,10 @@
         <v>2.1857</v>
       </c>
       <c r="D19" s="3">
-        <v>6.099</v>
+        <v>6.6328</v>
       </c>
       <c r="E19" s="3">
-        <v>3.9133</v>
+        <v>4.4471</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4710,10 +4710,10 @@
         <v>2.251</v>
       </c>
       <c r="D20" s="3">
-        <v>5.8761</v>
+        <v>5.6352</v>
       </c>
       <c r="E20" s="3">
-        <v>3.6251</v>
+        <v>3.3842</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4727,10 +4727,10 @@
         <v>1.9467</v>
       </c>
       <c r="D21" s="3">
-        <v>5.8722</v>
+        <v>5.7929</v>
       </c>
       <c r="E21" s="3">
-        <v>3.9255</v>
+        <v>3.8462</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4744,10 +4744,10 @@
         <v>1.221</v>
       </c>
       <c r="D22" s="3">
-        <v>6.4374</v>
+        <v>7.4309</v>
       </c>
       <c r="E22" s="3">
-        <v>5.2164</v>
+        <v>6.2099</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>6.6255</v>
+        <v>7.2621</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -4778,7 +4778,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>7.0196</v>
+        <v>7.92</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -4795,7 +4795,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>7.0622</v>
+        <v>7.4088</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -4812,7 +4812,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>7.3471</v>
+        <v>7.9641</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -4829,7 +4829,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>7.3078</v>
+        <v>7.422</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -4846,7 +4846,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>7.5313</v>
+        <v>7.968</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -4863,7 +4863,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>7.4459</v>
+        <v>7.4232</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -4880,7 +4880,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>7.635</v>
+        <v>7.9684</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -4897,7 +4897,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>7.5237</v>
+        <v>7.4233</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -4949,10 +4949,10 @@
         <v>0.2707</v>
       </c>
       <c r="D4" s="3">
-        <v>0.2399</v>
+        <v>0.1846</v>
       </c>
       <c r="E4" s="3">
-        <v>-0.0308</v>
+        <v>-0.0861</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4966,10 +4966,10 @@
         <v>0.1318</v>
       </c>
       <c r="D5" s="3">
-        <v>0.222</v>
+        <v>0.1731</v>
       </c>
       <c r="E5" s="3">
-        <v>0.0902</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4983,10 +4983,10 @@
         <v>0.3793</v>
       </c>
       <c r="D6" s="3">
-        <v>0.1974</v>
+        <v>0.1384</v>
       </c>
       <c r="E6" s="3">
-        <v>-0.1819</v>
+        <v>-0.2409</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5000,10 +5000,10 @@
         <v>0.4023</v>
       </c>
       <c r="D7" s="3">
-        <v>0.1833</v>
+        <v>0.1401</v>
       </c>
       <c r="E7" s="3">
-        <v>-0.219</v>
+        <v>-0.2622</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5017,10 +5017,10 @@
         <v>0.4892</v>
       </c>
       <c r="D8" s="3">
-        <v>0.1646</v>
+        <v>0.1181</v>
       </c>
       <c r="E8" s="3">
-        <v>-0.3246</v>
+        <v>-0.3711</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5034,10 +5034,10 @@
         <v>0.2327</v>
       </c>
       <c r="D9" s="3">
-        <v>0.1539</v>
+        <v>0.1207</v>
       </c>
       <c r="E9" s="3">
-        <v>-0.0788</v>
+        <v>-0.112</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5051,10 +5051,10 @@
         <v>0.4718</v>
       </c>
       <c r="D10" s="3">
-        <v>0.1569</v>
+        <v>0.1522</v>
       </c>
       <c r="E10" s="3">
-        <v>-0.3148</v>
+        <v>-0.3196</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5068,10 +5068,10 @@
         <v>0.2345</v>
       </c>
       <c r="D11" s="3">
-        <v>0.1624</v>
+        <v>0.1709</v>
       </c>
       <c r="E11" s="3">
-        <v>-0.0721</v>
+        <v>-0.0636</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5085,10 +5085,10 @@
         <v>0.3962</v>
       </c>
       <c r="D12" s="3">
-        <v>0.1658</v>
+        <v>0.1746</v>
       </c>
       <c r="E12" s="3">
-        <v>-0.2304</v>
+        <v>-0.2216</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5102,10 +5102,10 @@
         <v>0.324</v>
       </c>
       <c r="D13" s="3">
-        <v>0.1684</v>
+        <v>0.1757</v>
       </c>
       <c r="E13" s="3">
-        <v>-0.1556</v>
+        <v>-0.1483</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5119,10 +5119,10 @@
         <v>0.3668</v>
       </c>
       <c r="D14" s="3">
-        <v>0.1584</v>
+        <v>0.1426</v>
       </c>
       <c r="E14" s="3">
-        <v>-0.2084</v>
+        <v>-0.2242</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5136,10 +5136,10 @@
         <v>0.2775</v>
       </c>
       <c r="D15" s="3">
-        <v>0.1509</v>
+        <v>0.1327</v>
       </c>
       <c r="E15" s="3">
-        <v>-0.1266</v>
+        <v>-0.1448</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5153,10 +5153,10 @@
         <v>0.517</v>
       </c>
       <c r="D16" s="3">
-        <v>0.1679</v>
+        <v>0.193</v>
       </c>
       <c r="E16" s="3">
-        <v>-0.3491</v>
+        <v>-0.324</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5170,10 +5170,10 @@
         <v>0.3653</v>
       </c>
       <c r="D17" s="3">
-        <v>0.1847</v>
+        <v>0.2225</v>
       </c>
       <c r="E17" s="3">
-        <v>-0.1806</v>
+        <v>-0.1428</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5187,10 +5187,10 @@
         <v>0.409</v>
       </c>
       <c r="D18" s="3">
-        <v>0.1899</v>
+        <v>0.2104</v>
       </c>
       <c r="E18" s="3">
-        <v>-0.2191</v>
+        <v>-0.1986</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5204,10 +5204,10 @@
         <v>0.3383</v>
       </c>
       <c r="D19" s="3">
-        <v>0.198</v>
+        <v>0.2189</v>
       </c>
       <c r="E19" s="3">
-        <v>-0.1403</v>
+        <v>-0.1194</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5221,10 +5221,10 @@
         <v>0.3935</v>
       </c>
       <c r="D20" s="3">
-        <v>0.1848</v>
+        <v>0.1673</v>
       </c>
       <c r="E20" s="3">
-        <v>-0.2087</v>
+        <v>-0.2262</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5238,10 +5238,10 @@
         <v>0.1585</v>
       </c>
       <c r="D21" s="3">
-        <v>0.1782</v>
+        <v>0.161</v>
       </c>
       <c r="E21" s="3">
-        <v>0.0197</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5255,10 +5255,10 @@
         <v>0.5087</v>
       </c>
       <c r="D22" s="3">
-        <v>0.1938</v>
+        <v>0.2167</v>
       </c>
       <c r="E22" s="3">
-        <v>-0.3149</v>
+        <v>-0.292</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5272,7 +5272,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>0.1907</v>
+        <v>0.1921</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -5289,7 +5289,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>0.1935</v>
+        <v>0.199</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -5306,7 +5306,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>0.1905</v>
+        <v>0.1868</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -5323,7 +5323,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>0.1934</v>
+        <v>0.1974</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -5340,7 +5340,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>0.1904</v>
+        <v>0.1863</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -5357,7 +5357,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>0.1933</v>
+        <v>0.1972</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -5374,7 +5374,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>0.1904</v>
+        <v>0.1863</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -5391,7 +5391,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>0.1933</v>
+        <v>0.1972</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -5408,7 +5408,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>0.1903</v>
+        <v>0.1863</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -5460,10 +5460,10 @@
         <v>12.47</v>
       </c>
       <c r="D4" s="3">
-        <v>13.1244</v>
+        <v>14.3022</v>
       </c>
       <c r="E4" s="3">
-        <v>0.6544</v>
+        <v>1.8322</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5477,10 +5477,10 @@
         <v>11.58</v>
       </c>
       <c r="D5" s="3">
-        <v>14.7149</v>
+        <v>17.9312</v>
       </c>
       <c r="E5" s="3">
-        <v>3.1349</v>
+        <v>6.3512</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5494,10 +5494,10 @@
         <v>13.52</v>
       </c>
       <c r="D6" s="3">
-        <v>14.3573</v>
+        <v>14.6786</v>
       </c>
       <c r="E6" s="3">
-        <v>0.8373</v>
+        <v>1.1586</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5511,10 +5511,10 @@
         <v>16.1</v>
       </c>
       <c r="D7" s="3">
-        <v>15.0199</v>
+        <v>16.309</v>
       </c>
       <c r="E7" s="3">
-        <v>-1.0801</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5528,10 +5528,10 @@
         <v>16.3</v>
       </c>
       <c r="D8" s="3">
-        <v>13.9712</v>
+        <v>12.4703</v>
       </c>
       <c r="E8" s="3">
-        <v>-2.3288</v>
+        <v>-3.8297</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5545,10 +5545,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="3">
-        <v>13.8956</v>
+        <v>13.3093</v>
       </c>
       <c r="E9" s="3">
-        <v>-5.1044</v>
+        <v>-5.6907</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5562,10 +5562,10 @@
         <v>11.03</v>
       </c>
       <c r="D10" s="3">
-        <v>13.2248</v>
+        <v>11.8415</v>
       </c>
       <c r="E10" s="3">
-        <v>2.1948</v>
+        <v>0.8115</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5579,10 +5579,10 @@
         <v>16.5</v>
       </c>
       <c r="D11" s="3">
-        <v>13.4327</v>
+        <v>13.3918</v>
       </c>
       <c r="E11" s="3">
-        <v>-3.0673</v>
+        <v>-3.1082</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5596,10 +5596,10 @@
         <v>18.33</v>
       </c>
       <c r="D12" s="3">
-        <v>11.1995</v>
+        <v>7.1675</v>
       </c>
       <c r="E12" s="3">
-        <v>-7.1305</v>
+        <v>-11.1625</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5613,10 +5613,10 @@
         <v>15.02</v>
       </c>
       <c r="D13" s="3">
-        <v>9.5246</v>
+        <v>5.3002</v>
       </c>
       <c r="E13" s="3">
-        <v>-5.4954</v>
+        <v>-9.719799999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5630,10 +5630,10 @@
         <v>18.9</v>
       </c>
       <c r="D14" s="3">
-        <v>8.247</v>
+        <v>4.68</v>
       </c>
       <c r="E14" s="3">
-        <v>-10.653</v>
+        <v>-14.22</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5647,10 +5647,10 @@
         <v>14.65</v>
       </c>
       <c r="D15" s="3">
-        <v>7.2888</v>
+        <v>4.494</v>
       </c>
       <c r="E15" s="3">
-        <v>-7.3612</v>
+        <v>-10.156</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5664,10 +5664,10 @@
         <v>12.4</v>
       </c>
       <c r="D16" s="3">
-        <v>8.9894</v>
+        <v>11.2119</v>
       </c>
       <c r="E16" s="3">
-        <v>-3.4106</v>
+        <v>-1.1881</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5681,10 +5681,10 @@
         <v>14.37</v>
       </c>
       <c r="D17" s="3">
-        <v>11.1377</v>
+        <v>15.6714</v>
       </c>
       <c r="E17" s="3">
-        <v>-3.2323</v>
+        <v>1.3014</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5698,10 +5698,10 @@
         <v>14.17</v>
       </c>
       <c r="D18" s="3">
-        <v>11.7141</v>
+        <v>14.1117</v>
       </c>
       <c r="E18" s="3">
-        <v>-2.4559</v>
+        <v>-0.0583</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5715,10 +5715,10 @@
         <v>14.98</v>
       </c>
       <c r="D19" s="3">
-        <v>13.0712</v>
+        <v>16.2332</v>
       </c>
       <c r="E19" s="3">
-        <v>-1.9088</v>
+        <v>1.2532</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5732,10 +5732,10 @@
         <v>14.88</v>
       </c>
       <c r="D20" s="3">
-        <v>12.7205</v>
+        <v>13.0378</v>
       </c>
       <c r="E20" s="3">
-        <v>-2.1595</v>
+        <v>-1.8422</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5749,10 +5749,10 @@
         <v>12.65</v>
       </c>
       <c r="D21" s="3">
-        <v>13.1634</v>
+        <v>14.056</v>
       </c>
       <c r="E21" s="3">
-        <v>0.5134</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5766,10 +5766,10 @@
         <v>10.15</v>
       </c>
       <c r="D22" s="3">
-        <v>15.008</v>
+        <v>18.5961</v>
       </c>
       <c r="E22" s="3">
-        <v>4.858</v>
+        <v>8.446099999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5783,7 +5783,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>15.1145</v>
+        <v>16.3824</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -5800,7 +5800,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>16.289</v>
+        <v>18.7835</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -5817,7 +5817,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>16.0752</v>
+        <v>16.4387</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -5834,7 +5834,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>17.0095</v>
+        <v>18.8004</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -5851,7 +5851,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>16.6156</v>
+        <v>16.4437</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -5868,7 +5868,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>17.4148</v>
+        <v>18.8019</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -5885,7 +5885,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>16.9195</v>
+        <v>16.4442</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -5902,7 +5902,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>17.6428</v>
+        <v>18.8021</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -5919,7 +5919,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>17.0905</v>
+        <v>16.4442</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -5971,10 +5971,10 @@
         <v>498.6667</v>
       </c>
       <c r="D4" s="3">
-        <v>589.7595</v>
+        <v>753.7267000000001</v>
       </c>
       <c r="E4" s="3">
-        <v>91.0928</v>
+        <v>255.06</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5988,10 +5988,10 @@
         <v>305.8</v>
       </c>
       <c r="D5" s="3">
-        <v>737.093</v>
+        <v>1051.4834</v>
       </c>
       <c r="E5" s="3">
-        <v>431.293</v>
+        <v>745.6834</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6005,10 +6005,10 @@
         <v>438.8333</v>
       </c>
       <c r="D6" s="3">
-        <v>738.1724</v>
+        <v>834.4324</v>
       </c>
       <c r="E6" s="3">
-        <v>299.3391</v>
+        <v>395.5991</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6022,10 +6022,10 @@
         <v>469.6667</v>
       </c>
       <c r="D7" s="3">
-        <v>805.8577</v>
+        <v>956.5691</v>
       </c>
       <c r="E7" s="3">
-        <v>336.191</v>
+        <v>486.9024</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6039,10 +6039,10 @@
         <v>597.6</v>
       </c>
       <c r="D8" s="3">
-        <v>750.2536</v>
+        <v>695.3799</v>
       </c>
       <c r="E8" s="3">
-        <v>152.6536</v>
+        <v>97.7799</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6056,10 +6056,10 @@
         <v>715.3333</v>
       </c>
       <c r="D9" s="3">
-        <v>759.628</v>
+        <v>760.0397</v>
       </c>
       <c r="E9" s="3">
-        <v>44.2947</v>
+        <v>44.7064</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6073,10 +6073,10 @@
         <v>588.0234</v>
       </c>
       <c r="D10" s="3">
-        <v>716.9713</v>
+        <v>640.3128</v>
       </c>
       <c r="E10" s="3">
-        <v>128.9479</v>
+        <v>52.2894</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6090,10 +6090,10 @@
         <v>853.6667</v>
       </c>
       <c r="D11" s="3">
-        <v>736.0561</v>
+        <v>747.4113</v>
       </c>
       <c r="E11" s="3">
-        <v>-117.6106</v>
+        <v>-106.2554</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6107,10 +6107,10 @@
         <v>1152.1667</v>
       </c>
       <c r="D12" s="3">
-        <v>572.8255</v>
+        <v>282.4168</v>
       </c>
       <c r="E12" s="3">
-        <v>-579.3412</v>
+        <v>-869.7499</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6124,10 +6124,10 @@
         <v>707.6</v>
       </c>
       <c r="D13" s="3">
-        <v>450.4025</v>
+        <v>142.9185</v>
       </c>
       <c r="E13" s="3">
-        <v>-257.1975</v>
+        <v>-564.6815</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6141,10 +6141,10 @@
         <v>968</v>
       </c>
       <c r="D14" s="3">
-        <v>356.2455</v>
+        <v>94.5179</v>
       </c>
       <c r="E14" s="3">
-        <v>-611.7545</v>
+        <v>-873.4820999999999</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6158,10 +6158,10 @@
         <v>823</v>
       </c>
       <c r="D15" s="3">
-        <v>285.6278</v>
+        <v>79.99769999999999</v>
       </c>
       <c r="E15" s="3">
-        <v>-537.3722</v>
+        <v>-743.0023</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6175,10 +6175,10 @@
         <v>762.5</v>
       </c>
       <c r="D16" s="3">
-        <v>394.57</v>
+        <v>528.9767000000001</v>
       </c>
       <c r="E16" s="3">
-        <v>-367.93</v>
+        <v>-233.5233</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6192,10 +6192,10 @@
         <v>1096</v>
       </c>
       <c r="D17" s="3">
-        <v>521.7147</v>
+        <v>790.8972</v>
       </c>
       <c r="E17" s="3">
-        <v>-574.2853</v>
+        <v>-305.1028</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6209,10 +6209,10 @@
         <v>1100</v>
       </c>
       <c r="D18" s="3">
-        <v>548.401</v>
+        <v>677.1911</v>
       </c>
       <c r="E18" s="3">
-        <v>-551.599</v>
+        <v>-422.8089</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6226,10 +6226,10 @@
         <v>869.5</v>
       </c>
       <c r="D19" s="3">
-        <v>623.1257000000001</v>
+        <v>796.2672</v>
       </c>
       <c r="E19" s="3">
-        <v>-246.3743</v>
+        <v>-73.2328</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6243,10 +6243,10 @@
         <v>593.5333000000001</v>
       </c>
       <c r="D20" s="3">
-        <v>627.2762</v>
+        <v>686.6896</v>
       </c>
       <c r="E20" s="3">
-        <v>33.7429</v>
+        <v>93.1563</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6260,10 +6260,10 @@
         <v>683</v>
       </c>
       <c r="D21" s="3">
-        <v>686.2145</v>
+        <v>810.1274</v>
       </c>
       <c r="E21" s="3">
-        <v>3.2145</v>
+        <v>127.1274</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6277,10 +6277,10 @@
         <v>724.6667</v>
       </c>
       <c r="D22" s="3">
-        <v>804.151</v>
+        <v>1053.6107</v>
       </c>
       <c r="E22" s="3">
-        <v>79.4843</v>
+        <v>328.944</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6294,7 +6294,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>819.8645</v>
+        <v>922.9866</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -6311,7 +6311,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>910.3016</v>
+        <v>1104.0251</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -6328,7 +6328,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>899.4774</v>
+        <v>938.1109</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -6345,7 +6345,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>970.0113</v>
+        <v>1108.5624</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -6362,7 +6362,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>944.2597</v>
+        <v>939.4721</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -6379,7 +6379,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>1003.598</v>
+        <v>1108.9708</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -6396,7 +6396,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>969.4497</v>
+        <v>939.5946</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -6413,7 +6413,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>1022.4906</v>
+        <v>1109.0075</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -6430,7 +6430,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>983.6191</v>
+        <v>939.6056</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
@@ -6482,10 +6482,10 @@
         <v>196.6667</v>
       </c>
       <c r="D4" s="3">
-        <v>232.5953</v>
+        <v>297.2668</v>
       </c>
       <c r="E4" s="3">
-        <v>35.9286</v>
+        <v>100.6001</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6499,10 +6499,10 @@
         <v>111</v>
       </c>
       <c r="D5" s="3">
-        <v>289.7322</v>
+        <v>411.9801</v>
       </c>
       <c r="E5" s="3">
-        <v>178.7322</v>
+        <v>300.9801</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6516,10 +6516,10 @@
         <v>187.1667</v>
       </c>
       <c r="D6" s="3">
-        <v>291.2325</v>
+        <v>330.6075</v>
       </c>
       <c r="E6" s="3">
-        <v>104.0658</v>
+        <v>143.4408</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6533,10 +6533,10 @@
         <v>174.3333</v>
       </c>
       <c r="D7" s="3">
-        <v>317.9104</v>
+        <v>377.7431</v>
       </c>
       <c r="E7" s="3">
-        <v>143.5771</v>
+        <v>203.4098</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6550,10 +6550,10 @@
         <v>249.4</v>
       </c>
       <c r="D8" s="3">
-        <v>297.6145</v>
+        <v>279.0316</v>
       </c>
       <c r="E8" s="3">
-        <v>48.2145</v>
+        <v>29.6316</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6567,10 +6567,10 @@
         <v>276</v>
       </c>
       <c r="D9" s="3">
-        <v>301.9087</v>
+        <v>304.0635</v>
       </c>
       <c r="E9" s="3">
-        <v>25.9087</v>
+        <v>28.0635</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6584,10 +6584,10 @@
         <v>226.75</v>
       </c>
       <c r="D10" s="3">
-        <v>286.2908</v>
+        <v>258.8249</v>
       </c>
       <c r="E10" s="3">
-        <v>59.5408</v>
+        <v>32.0749</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6601,10 +6601,10 @@
         <v>335</v>
       </c>
       <c r="D11" s="3">
-        <v>294.0935</v>
+        <v>299.8987</v>
       </c>
       <c r="E11" s="3">
-        <v>-40.9065</v>
+        <v>-35.1013</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6618,10 +6618,10 @@
         <v>450.8333</v>
       </c>
       <c r="D12" s="3">
-        <v>232.3311</v>
+        <v>122.9002</v>
       </c>
       <c r="E12" s="3">
-        <v>-218.5022</v>
+        <v>-327.9331</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6635,10 +6635,10 @@
         <v>270</v>
       </c>
       <c r="D13" s="3">
-        <v>186.0092</v>
+        <v>69.8006</v>
       </c>
       <c r="E13" s="3">
-        <v>-83.99079999999999</v>
+        <v>-200.1994</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6652,10 +6652,10 @@
         <v>360.75</v>
       </c>
       <c r="D14" s="3">
-        <v>149.9273</v>
+        <v>50.1172</v>
       </c>
       <c r="E14" s="3">
-        <v>-210.8227</v>
+        <v>-310.6328</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6669,10 +6669,10 @@
         <v>384.75</v>
       </c>
       <c r="D15" s="3">
-        <v>122.8658</v>
+        <v>44.2122</v>
       </c>
       <c r="E15" s="3">
-        <v>-261.8842</v>
+        <v>-340.5378</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6686,10 +6686,10 @@
         <v>320</v>
       </c>
       <c r="D16" s="3">
-        <v>163.7599</v>
+        <v>213.7731</v>
       </c>
       <c r="E16" s="3">
-        <v>-156.2401</v>
+        <v>-106.2269</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6703,10 +6703,10 @@
         <v>354</v>
       </c>
       <c r="D17" s="3">
-        <v>212.3196</v>
+        <v>314.731</v>
       </c>
       <c r="E17" s="3">
-        <v>-141.6804</v>
+        <v>-39.269</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6720,10 +6720,10 @@
         <v>398.3333</v>
       </c>
       <c r="D18" s="3">
-        <v>222.4809</v>
+        <v>271.4947</v>
       </c>
       <c r="E18" s="3">
-        <v>-175.8524</v>
+        <v>-126.8386</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6737,10 +6737,10 @@
         <v>310.6667</v>
       </c>
       <c r="D19" s="3">
-        <v>251.3645</v>
+        <v>318.0591</v>
       </c>
       <c r="E19" s="3">
-        <v>-59.3022</v>
+        <v>7.3924</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6754,10 +6754,10 @@
         <v>345</v>
       </c>
       <c r="D20" s="3">
-        <v>252.0869</v>
+        <v>273.3956</v>
       </c>
       <c r="E20" s="3">
-        <v>-92.9131</v>
+        <v>-71.6044</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6771,10 +6771,10 @@
         <v>251.25</v>
       </c>
       <c r="D21" s="3">
-        <v>273.8032</v>
+        <v>319.2853</v>
       </c>
       <c r="E21" s="3">
-        <v>22.5532</v>
+        <v>68.03530000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6788,10 +6788,10 @@
         <v>270</v>
       </c>
       <c r="D22" s="3">
-        <v>321.2218</v>
+        <v>420.22</v>
       </c>
       <c r="E22" s="3">
-        <v>51.2218</v>
+        <v>150.22</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6805,7 +6805,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>327.0328</v>
+        <v>367.192</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>7</v>
@@ -6822,7 +6822,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>361.4433</v>
+        <v>435.4299</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>7</v>
@@ -6839,7 +6839,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="3">
-        <v>357.1989</v>
+        <v>371.755</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>7</v>
@@ -6856,7 +6856,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="3">
-        <v>384.0679</v>
+        <v>436.7988</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -6873,7 +6873,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="3">
-        <v>374.1673</v>
+        <v>372.1657</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>7</v>
@@ -6890,7 +6890,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>396.7942</v>
+        <v>436.922</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>7</v>
@@ -6907,7 +6907,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="3">
-        <v>383.7121</v>
+        <v>372.2026</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>7</v>
@@ -6924,7 +6924,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="3">
-        <v>403.9527</v>
+        <v>436.9331</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -6941,7 +6941,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="3">
-        <v>389.081</v>
+        <v>372.2059</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>7</v>
